--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22480" windowHeight="9690"/>
+    <workbookView windowWidth="24930" windowHeight="10610"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="101">
   <si>
     <t>ID</t>
   </si>
@@ -46,7 +46,7 @@
     <t>TargetType</t>
   </si>
   <si>
-    <t>CD</t>
+    <t>Cd</t>
   </si>
   <si>
     <t>SpellRange</t>
@@ -91,19 +91,19 @@
     <t>HitDelay</t>
   </si>
   <si>
-    <t>BUFF</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>AP</t>
-  </si>
-  <si>
-    <t>ADC</t>
-  </si>
-  <si>
-    <t>APC</t>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>Ad</t>
+  </si>
+  <si>
+    <t>Ap</t>
+  </si>
+  <si>
+    <t>Adc</t>
+  </si>
+  <si>
+    <t>Apc</t>
   </si>
   <si>
     <t>int</t>
@@ -116,12 +116,6 @@
   </si>
   <si>
     <t>bool</t>
-  </si>
-  <si>
-    <t>float[]</t>
-  </si>
-  <si>
-    <t>int[]</t>
   </si>
   <si>
     <t>编号</t>
@@ -335,7 +329,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,13 +339,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -503,7 +490,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -579,12 +566,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,48 +802,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -872,97 +856,94 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1462,7 +1443,7 @@
         <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>32</v>
@@ -1501,10 +1482,10 @@
         <v>32</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>32</v>
@@ -1521,94 +1502,94 @@
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:30">
       <c r="A3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:30">
@@ -1622,10 +1603,10 @@
         <v>1001</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -1634,19 +1615,19 @@
         <v>3</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="K4" s="4">
         <v>1.5</v>
       </c>
       <c r="L4" s="4">
-        <v>3500</v>
+        <v>3.5</v>
       </c>
       <c r="M4" s="4">
         <v>0</v>
@@ -1655,10 +1636,10 @@
         <v>0</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="4">
         <v>0</v>
@@ -1670,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V4" s="4">
         <v>0</v>
@@ -1682,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AA4" s="4">
         <v>20</v>
@@ -1708,10 +1689,10 @@
         <v>1002</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -1720,19 +1701,19 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K5" s="4">
         <v>5</v>
       </c>
       <c r="L5" s="4">
-        <v>3500</v>
+        <v>3.5</v>
       </c>
       <c r="M5" s="4">
         <v>0</v>
@@ -1741,10 +1722,10 @@
         <v>20</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q5" s="4">
         <v>5</v>
@@ -1756,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V5" s="4">
         <v>0</v>
@@ -1768,10 +1749,10 @@
         <v>0</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AA5" s="4">
         <v>40</v>
@@ -1797,10 +1778,10 @@
         <v>1003</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1809,13 +1790,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K6" s="4">
         <v>3.5</v>
@@ -1830,10 +1811,10 @@
         <v>25</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="4">
         <v>10</v>
@@ -1845,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V6" s="4">
         <v>4000</v>
@@ -1857,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AA6" s="4">
         <v>60</v>
@@ -1883,10 +1864,10 @@
         <v>2001</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1895,19 +1876,19 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="K7" s="4">
         <v>1.5</v>
       </c>
       <c r="L7" s="4">
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="M7" s="4">
         <v>0.9</v>
@@ -1916,10 +1897,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q7" s="4">
         <v>0</v>
@@ -1931,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V7" s="4">
         <v>0</v>
@@ -1958,10 +1939,10 @@
         <v>2002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1970,19 +1951,19 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K8" s="4">
         <v>5</v>
       </c>
       <c r="L8" s="4">
-        <v>20000</v>
+        <v>20</v>
       </c>
       <c r="M8" s="4">
         <v>1.5</v>
@@ -1991,10 +1972,10 @@
         <v>35</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
@@ -2003,13 +1984,13 @@
         <v>1</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T8" s="4">
         <v>15000</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V8" s="4">
         <v>4000</v>
@@ -2021,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AB8" s="4">
         <v>0</v>
@@ -2042,10 +2023,10 @@
         <v>2003</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -2054,19 +2035,19 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K9" s="4">
         <v>5</v>
       </c>
       <c r="L9" s="4">
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="M9" s="4">
         <v>1.5</v>
@@ -2075,10 +2056,10 @@
         <v>35</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2090,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V9" s="4">
         <v>0</v>
@@ -2102,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AA9" s="4">
         <v>0</v>
@@ -2128,10 +2109,10 @@
         <v>101</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2140,19 +2121,19 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="K10" s="4">
         <v>2</v>
       </c>
       <c r="L10" s="4">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="M10" s="4">
         <v>0</v>
@@ -2161,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q10" s="4">
         <v>0</v>
@@ -2173,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="V10" s="4">
         <v>0</v>
@@ -2185,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AA10" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24930" windowHeight="10610"/>
+    <workbookView windowWidth="22700" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
@@ -220,7 +220,7 @@
     <t>Icons/skill_icon_04</t>
   </si>
   <si>
-    <t>单位</t>
+    <t>Unit</t>
   </si>
   <si>
     <t>Attack</t>
@@ -304,7 +304,7 @@
     <t>自定义技能</t>
   </si>
   <si>
-    <t>点</t>
+    <t>Position</t>
   </si>
   <si>
     <t>野怪近战[物理]</t>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22700" windowHeight="8200"/>
+    <workbookView windowWidth="22700" windowHeight="6640"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Type</t>
   </si>
   <si>
+    <t>HitCheck</t>
+  </si>
+  <si>
     <t>Icon</t>
   </si>
   <si>
@@ -142,6 +145,9 @@
     <t>类别</t>
   </si>
   <si>
+    <t>命中检查</t>
+  </si>
+  <si>
     <t>技能图标</t>
   </si>
   <si>
@@ -208,13 +214,34 @@
     <t>法攻加成</t>
   </si>
   <si>
+    <t>剑士基础连招一</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>剑士基础连招二</t>
+  </si>
+  <si>
+    <t>剑士基础连招三</t>
+  </si>
+  <si>
     <t>横剑击</t>
   </si>
   <si>
     <t>剑士的基础招式，无消耗</t>
   </si>
   <si>
-    <t>普通攻击</t>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Server</t>
   </si>
   <si>
     <t>Icons/skill_icon_04</t>
@@ -238,9 +265,6 @@
     <t>对单个目标造成物理攻击，添加流血效果</t>
   </si>
   <si>
-    <t>技能</t>
-  </si>
-  <si>
     <t>Icons/skill_icon_02</t>
   </si>
   <si>
@@ -257,9 +281,6 @@
   </si>
   <si>
     <t>Icons/skill_icon_03</t>
-  </si>
-  <si>
-    <t>None</t>
   </si>
   <si>
     <t>Spell</t>
@@ -947,7 +968,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -966,6 +987,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1286,7 +1310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1294,29 +1318,30 @@
     <col min="5" max="5" width="34.625" style="4" customWidth="1"/>
     <col min="6" max="7" width="9.375" style="4" customWidth="1"/>
     <col min="8" max="8" width="10.75" style="4" customWidth="1"/>
-    <col min="9" max="9" width="17.75" style="4" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="9" style="4"/>
-    <col min="12" max="12" width="12" style="4" customWidth="1"/>
-    <col min="13" max="13" width="15.75" style="4" customWidth="1"/>
-    <col min="14" max="14" width="9" style="4"/>
-    <col min="15" max="15" width="12.875" style="4" customWidth="1"/>
-    <col min="16" max="16" width="31.125" style="4" customWidth="1"/>
-    <col min="17" max="18" width="10.875" style="4" customWidth="1"/>
-    <col min="19" max="19" width="25.25" style="4" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="4" customWidth="1"/>
-    <col min="21" max="21" width="35.75" style="4" customWidth="1"/>
-    <col min="22" max="22" width="9.625" style="4" customWidth="1"/>
-    <col min="23" max="23" width="10.25" style="4" customWidth="1"/>
-    <col min="24" max="24" width="17.05" style="4" customWidth="1"/>
-    <col min="25" max="25" width="18.125" style="4" customWidth="1"/>
-    <col min="26" max="26" width="9" style="4" customWidth="1"/>
-    <col min="27" max="28" width="9" style="4"/>
-    <col min="29" max="29" width="12" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="4"/>
+    <col min="9" max="9" width="14.4166666666667" style="4" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="4" customWidth="1"/>
+    <col min="12" max="12" width="9" style="4"/>
+    <col min="13" max="13" width="12" style="4" customWidth="1"/>
+    <col min="14" max="14" width="15.75" style="4" customWidth="1"/>
+    <col min="15" max="15" width="9" style="4"/>
+    <col min="16" max="16" width="12.875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="31.125" style="4" customWidth="1"/>
+    <col min="18" max="19" width="10.875" style="4" customWidth="1"/>
+    <col min="20" max="20" width="25.25" style="4" customWidth="1"/>
+    <col min="21" max="21" width="12.75" style="4" customWidth="1"/>
+    <col min="22" max="22" width="35.75" style="4" customWidth="1"/>
+    <col min="23" max="23" width="9.625" style="4" customWidth="1"/>
+    <col min="24" max="24" width="10.25" style="4" customWidth="1"/>
+    <col min="25" max="25" width="17.05" style="4" customWidth="1"/>
+    <col min="26" max="26" width="18.125" style="4" customWidth="1"/>
+    <col min="27" max="27" width="9" style="4" customWidth="1"/>
+    <col min="28" max="29" width="9" style="4"/>
+    <col min="30" max="30" width="12" customWidth="1"/>
+    <col min="31" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:30">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1407,542 +1432,492 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:30">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:31">
       <c r="A2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="S2" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:30">
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:31">
       <c r="A3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:30">
+    <row r="4" customHeight="1" spans="1:31">
       <c r="A4" s="3">
+        <v>101</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>101</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4"/>
+      <c r="AB4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:31">
+      <c r="A5" s="3">
+        <v>102</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>102</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4"/>
+      <c r="AB5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:31">
+      <c r="A6" s="3">
+        <v>103</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>103</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:31">
+      <c r="A7" s="3">
         <v>1001</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
         <v>1001</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="D7" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4">
         <v>3</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" s="4">
+      <c r="H7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" s="4">
         <v>1.5</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M7" s="4">
         <v>3.5</v>
       </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4" s="4">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4">
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
         <v>0.85</v>
       </c>
-      <c r="X4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA4" s="4">
+      <c r="Y7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB7" s="4">
         <v>20</v>
       </c>
-      <c r="AB4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="4">
+      <c r="AC7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
         <v>0.8</v>
       </c>
-      <c r="AD4" s="4">
+      <c r="AE7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:30">
-      <c r="A5" s="3">
+    <row r="8" customHeight="1" spans="1:31">
+      <c r="A8" s="3">
         <v>1002</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3">
         <v>1002</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="4">
-        <v>5</v>
-      </c>
-      <c r="L5" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <v>20</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>5</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="V5" s="4">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4">
-        <v>0.85</v>
-      </c>
-      <c r="X5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z5" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA5" s="4">
-        <v>40</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="AD5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:30">
-      <c r="A6" s="3">
-        <v>1003</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1003</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="K6" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="L6" s="4">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4">
-        <v>25</v>
-      </c>
-      <c r="O6" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>10</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="V6" s="4">
-        <v>4000</v>
-      </c>
-      <c r="W6" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="X6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA6" s="4">
-        <v>60</v>
-      </c>
-      <c r="AB6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="AD6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:30">
-      <c r="A7" s="3">
-        <v>2001</v>
-      </c>
-      <c r="B7" s="3">
-        <v>2</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2001</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K7" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="L7" s="4">
-        <v>10</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="N7" s="4">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="V7" s="4">
-        <v>0</v>
-      </c>
-      <c r="W7" s="4">
-        <v>0</v>
-      </c>
-      <c r="X7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:30">
-      <c r="A8" s="3">
-        <v>2002</v>
-      </c>
-      <c r="B8" s="3">
-        <v>2</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2002</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1954,79 +1929,87 @@
         <v>74</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="4">
+        <v>83</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="4">
         <v>5</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
         <v>20</v>
       </c>
-      <c r="M8" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="N8" s="4">
-        <v>35</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="P8" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q8" s="4">
+        <v>78</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R8" s="4">
         <v>5</v>
       </c>
-      <c r="R8" s="4">
-        <v>1</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="T8" s="4">
-        <v>15000</v>
-      </c>
-      <c r="U8" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="V8" s="4">
-        <v>4000</v>
+      <c r="S8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="W8" s="4">
         <v>0</v>
       </c>
       <c r="X8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>94</v>
+        <v>0.85</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="AB8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
       <c r="AD8" s="4">
-        <v>1</v>
+        <v>0.6</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:30">
+    <row r="9" customHeight="1" spans="1:31">
       <c r="A9" s="3">
-        <v>2003</v>
+        <v>1003</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3">
-        <v>2003</v>
+        <v>1003</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -2038,146 +2021,406 @@
         <v>74</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <v>25</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="R9" s="4">
+        <v>10</v>
+      </c>
+      <c r="S9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="W9" s="4">
+        <v>40</v>
+      </c>
+      <c r="X9" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>60</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:31">
+      <c r="A10" s="3">
+        <v>2001</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2001</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="E10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L10" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="M10" s="4">
+        <v>10</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U10" s="4">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="K9" s="4">
+      <c r="W10" s="4">
+        <v>0</v>
+      </c>
+      <c r="X10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:31">
+      <c r="A11" s="3">
+        <v>2002</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2002</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" s="4">
         <v>5</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M11" s="4">
+        <v>20</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="O11" s="4">
+        <v>35</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="R11" s="4">
+        <v>5</v>
+      </c>
+      <c r="S11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U11" s="4">
+        <v>15000</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="W11" s="4">
+        <v>40</v>
+      </c>
+      <c r="X11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:31">
+      <c r="A12" s="3">
+        <v>2003</v>
+      </c>
+      <c r="B12" s="3">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2003</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="4">
+        <v>5</v>
+      </c>
+      <c r="M12" s="4">
         <v>10</v>
       </c>
-      <c r="M9" s="4">
+      <c r="N12" s="4">
         <v>1.5</v>
       </c>
-      <c r="N9" s="4">
+      <c r="O12" s="4">
         <v>35</v>
       </c>
-      <c r="O9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q9" s="4">
+      <c r="P12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R12" s="4">
         <v>10</v>
       </c>
-      <c r="R9" s="4">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="V9" s="4">
-        <v>0</v>
-      </c>
-      <c r="W9" s="4">
-        <v>0</v>
-      </c>
-      <c r="X9" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="4">
+      <c r="S12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U12" s="4">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="W12" s="4">
+        <v>0</v>
+      </c>
+      <c r="X12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:30">
-      <c r="A10" s="3">
-        <v>101</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>101</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K10" s="4">
+    <row r="13" customHeight="1" spans="1:31">
+      <c r="A13" s="3">
+        <v>10001</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>10001</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="4">
         <v>2</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M13" s="4">
         <v>3</v>
       </c>
-      <c r="M10" s="4">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="V10" s="4">
-        <v>0</v>
-      </c>
-      <c r="W10" s="4">
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="W13" s="4">
+        <v>0</v>
+      </c>
+      <c r="X13" s="4">
         <v>0.85</v>
       </c>
-      <c r="X10" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA10" s="4">
+      <c r="Y13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB13" s="4">
         <v>50</v>
       </c>
-      <c r="AB10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="4">
+      <c r="AC13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="4">
         <v>0</v>
       </c>
     </row>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -1672,6 +1672,15 @@
       <c r="S4" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="U4" s="4">
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0</v>
+      </c>
       <c r="Y4" s="4">
         <v>0</v>
       </c>
@@ -1735,6 +1744,15 @@
       <c r="S5" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="U5" s="4">
+        <v>0</v>
+      </c>
+      <c r="W5" s="4">
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <v>0</v>
+      </c>
       <c r="Y5" s="4">
         <v>0</v>
       </c>
@@ -1798,6 +1816,15 @@
       <c r="S6" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0</v>
+      </c>
       <c r="Y6" s="4">
         <v>0</v>
       </c>
@@ -2224,7 +2251,7 @@
         <v>100</v>
       </c>
       <c r="U11" s="4">
-        <v>15000</v>
+        <v>150</v>
       </c>
       <c r="V11" s="4" t="s">
         <v>96</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22700" windowHeight="6640"/>
+    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="110">
   <si>
     <t>ID</t>
   </si>
@@ -40,9 +53,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>HitCheck</t>
-  </si>
-  <si>
     <t>Icon</t>
   </si>
   <si>
@@ -55,12 +65,12 @@
     <t>SpellRange</t>
   </si>
   <si>
+    <t>Cost</t>
+  </si>
+  <si>
     <t>IntonateTime</t>
   </si>
   <si>
-    <t>Cost</t>
-  </si>
-  <si>
     <t>Anim1</t>
   </si>
   <si>
@@ -85,12 +95,12 @@
     <t>Area</t>
   </si>
   <si>
+    <t>AreaOffset</t>
+  </si>
+  <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>Interval</t>
-  </si>
-  <si>
     <t>HitDelay</t>
   </si>
   <si>
@@ -145,9 +155,6 @@
     <t>类别</t>
   </si>
   <si>
-    <t>命中检查</t>
-  </si>
-  <si>
     <t>技能图标</t>
   </si>
   <si>
@@ -160,12 +167,12 @@
     <t>施法距离</t>
   </si>
   <si>
+    <t>魔法消耗</t>
+  </si>
+  <si>
     <t>施法前摇</t>
   </si>
   <si>
-    <t>魔法消耗</t>
-  </si>
-  <si>
     <t>前摇动作</t>
   </si>
   <si>
@@ -190,12 +197,12 @@
     <t>影响区域</t>
   </si>
   <si>
+    <t>区域偏移</t>
+  </si>
+  <si>
     <t>持续时间</t>
   </si>
   <si>
-    <t>伤害间隔</t>
-  </si>
-  <si>
     <t>命中延迟</t>
   </si>
   <si>
@@ -220,18 +227,33 @@
     <t>Normal</t>
   </si>
   <si>
-    <t>Client</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
+    <t>(0,1.2,1)</t>
+  </si>
+  <si>
+    <t>[0.3]</t>
+  </si>
+  <si>
     <t>剑士基础连招二</t>
   </si>
   <si>
+    <t>(0,1.3,0.3)</t>
+  </si>
+  <si>
+    <t>[0.1]</t>
+  </si>
+  <si>
     <t>剑士基础连招三</t>
   </si>
   <si>
+    <t>(0,1.7,0.4)</t>
+  </si>
+  <si>
+    <t>[0.7]</t>
+  </si>
+  <si>
     <t>横剑击</t>
   </si>
   <si>
@@ -239,9 +261,6 @@
   </si>
   <si>
     <t>Skill</t>
-  </si>
-  <si>
-    <t>Server</t>
   </si>
   <si>
     <t>Icons/skill_icon_04</t>
@@ -343,7 +362,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -367,34 +386,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -408,14 +399,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -455,6 +438,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -505,7 +503,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -526,49 +545,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,97 +683,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,21 +738,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -767,6 +771,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,152 +842,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -988,58 +1007,55 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1310,38 +1326,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
     <col min="4" max="4" width="14.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="34.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="36.1416666666667" style="4" customWidth="1"/>
     <col min="6" max="7" width="9.375" style="4" customWidth="1"/>
     <col min="8" max="8" width="10.75" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.4166666666667" style="4" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="4" customWidth="1"/>
-    <col min="12" max="12" width="9" style="4"/>
-    <col min="13" max="13" width="12" style="4" customWidth="1"/>
+    <col min="9" max="9" width="17.75" style="4" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="4" customWidth="1"/>
+    <col min="11" max="11" width="9" style="4"/>
+    <col min="12" max="12" width="12" style="4" customWidth="1"/>
+    <col min="13" max="13" width="9" style="4"/>
     <col min="14" max="14" width="15.75" style="4" customWidth="1"/>
-    <col min="15" max="15" width="9" style="4"/>
-    <col min="16" max="16" width="12.875" style="4" customWidth="1"/>
-    <col min="17" max="17" width="31.125" style="4" customWidth="1"/>
-    <col min="18" max="19" width="10.875" style="4" customWidth="1"/>
-    <col min="20" max="20" width="25.25" style="4" customWidth="1"/>
-    <col min="21" max="21" width="12.75" style="4" customWidth="1"/>
-    <col min="22" max="22" width="35.75" style="4" customWidth="1"/>
-    <col min="23" max="23" width="9.625" style="4" customWidth="1"/>
-    <col min="24" max="24" width="10.25" style="4" customWidth="1"/>
-    <col min="25" max="25" width="17.05" style="4" customWidth="1"/>
-    <col min="26" max="26" width="18.125" style="4" customWidth="1"/>
-    <col min="27" max="27" width="9" style="4" customWidth="1"/>
-    <col min="28" max="29" width="9" style="4"/>
-    <col min="30" max="30" width="12" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="4"/>
+    <col min="15" max="15" width="12.875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="31.125" style="4" customWidth="1"/>
+    <col min="17" max="18" width="10.875" style="4" customWidth="1"/>
+    <col min="19" max="19" width="25.25" style="4" customWidth="1"/>
+    <col min="20" max="20" width="12.75" style="4" customWidth="1"/>
+    <col min="21" max="21" width="35.75" style="4" customWidth="1"/>
+    <col min="22" max="22" width="9.625" style="4" customWidth="1"/>
+    <col min="23" max="24" width="10.25" style="4" customWidth="1"/>
+    <col min="25" max="25" width="18.125" style="4" customWidth="1"/>
+    <col min="26" max="26" width="9" style="4" customWidth="1"/>
+    <col min="27" max="28" width="9" style="4"/>
+    <col min="29" max="29" width="12" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:31">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1432,70 +1446,67 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:30">
+      <c r="A2" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:31">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>31</v>
@@ -1507,126 +1518,120 @@
         <v>31</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:31">
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:30">
       <c r="A3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AD3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>65</v>
-      </c>
     </row>
-    <row r="4" customHeight="1" spans="1:31">
+    <row r="4" customHeight="1" spans="1:30">
       <c r="A4" s="3">
         <v>101</v>
       </c>
@@ -1637,68 +1642,67 @@
         <v>101</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0</v>
+      </c>
+      <c r="V4" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="W4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="X4" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4">
-        <v>0</v>
-      </c>
-      <c r="W4" s="4">
-        <v>0</v>
-      </c>
-      <c r="X4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4"/>
+      <c r="AA4" s="4">
+        <v>0</v>
+      </c>
       <c r="AB4" s="4">
         <v>0</v>
       </c>
       <c r="AC4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="7">
         <v>0.8</v>
       </c>
-      <c r="AE4" s="4">
+      <c r="AD4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:31">
+    <row r="5" customHeight="1" spans="1:30">
       <c r="A5" s="3">
         <v>102</v>
       </c>
@@ -1709,68 +1713,67 @@
         <v>102</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="W5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="4">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5" s="4">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4">
-        <v>0</v>
-      </c>
       <c r="X5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4"/>
+        <v>0.3</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>0</v>
+      </c>
       <c r="AB5" s="4">
         <v>0</v>
       </c>
       <c r="AC5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="7">
         <v>0.7</v>
       </c>
-      <c r="AE5" s="4">
+      <c r="AD5" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:31">
+    <row r="6" customHeight="1" spans="1:30">
       <c r="A6" s="3">
         <v>103</v>
       </c>
@@ -1781,7 +1784,7 @@
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1790,13 +1793,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
       </c>
       <c r="L6" s="4">
         <v>0</v>
@@ -1807,41 +1810,41 @@
       <c r="N6" s="4">
         <v>0</v>
       </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4">
-        <v>0</v>
-      </c>
-      <c r="W6" s="4">
-        <v>0</v>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="X6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA6" s="4">
         <v>0</v>
       </c>
       <c r="AB6" s="4">
         <v>0</v>
       </c>
       <c r="AC6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="7">
         <v>1.2</v>
       </c>
-      <c r="AE6" s="4">
+      <c r="AD6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:31">
+    <row r="7" customHeight="1" spans="1:30">
       <c r="A7" s="3">
         <v>1001</v>
       </c>
@@ -1852,10 +1855,10 @@
         <v>1001</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1864,73 +1867,67 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="K7" s="4">
+        <v>1.5</v>
       </c>
       <c r="L7" s="4">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="M7" s="4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N7" s="4">
         <v>0</v>
       </c>
-      <c r="O7" s="4">
-        <v>0</v>
+      <c r="O7" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="4">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="W7" s="4">
+        <v>80</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="V7" s="4">
         <v>0</v>
       </c>
       <c r="X7" s="4">
         <v>0.85</v>
       </c>
-      <c r="Y7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4" t="s">
-        <v>80</v>
+      <c r="Y7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>20</v>
       </c>
       <c r="AB7" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AD7" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="AE7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:31">
+    <row r="8" customHeight="1" spans="1:30">
       <c r="A8" s="3">
         <v>1002</v>
       </c>
@@ -1941,88 +1938,82 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="4">
+        <v>5</v>
+      </c>
+      <c r="L8" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="M8" s="4">
+        <v>20</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>5</v>
+      </c>
+      <c r="R8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="4">
-        <v>5</v>
-      </c>
-      <c r="M8" s="4">
-        <v>3.5</v>
-      </c>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <v>20</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R8" s="4">
-        <v>5</v>
-      </c>
-      <c r="S8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4">
-        <v>0</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="W8" s="4">
+      <c r="V8" s="4">
         <v>0</v>
       </c>
       <c r="X8" s="4">
         <v>0.85</v>
       </c>
-      <c r="Y8" s="4">
-        <v>0</v>
+      <c r="Y8" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>40</v>
       </c>
       <c r="AB8" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AD8" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="AE8" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:31">
+    <row r="9" customHeight="1" spans="1:30">
       <c r="A9" s="3">
         <v>1003</v>
       </c>
@@ -2033,10 +2024,10 @@
         <v>1003</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -2045,73 +2036,67 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
+      </c>
+      <c r="K9" s="4">
+        <v>3.5</v>
       </c>
       <c r="L9" s="4">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M9" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N9" s="4">
         <v>0</v>
       </c>
-      <c r="O9" s="4">
-        <v>25</v>
+      <c r="O9" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="R9" s="4">
+        <v>92</v>
+      </c>
+      <c r="Q9" s="4">
         <v>10</v>
       </c>
-      <c r="S9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U9" s="4">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="W9" s="4">
+      <c r="R9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="V9" s="4">
         <v>40</v>
       </c>
       <c r="X9" s="4">
         <v>1.5</v>
       </c>
-      <c r="Y9" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>91</v>
+      <c r="Y9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>60</v>
       </c>
       <c r="AB9" s="4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AD9" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="AE9" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:31">
+    <row r="10" customHeight="1" spans="1:30">
       <c r="A10" s="3">
         <v>2001</v>
       </c>
@@ -2122,10 +2107,10 @@
         <v>2001</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2134,62 +2119,56 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="K10" s="4">
+        <v>1.5</v>
       </c>
       <c r="L10" s="4">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="M10" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N10" s="4">
         <v>0.9</v>
       </c>
-      <c r="O10" s="4">
-        <v>0</v>
+      <c r="O10" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="4">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="W10" s="4">
+        <v>97</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="V10" s="4">
         <v>0</v>
       </c>
       <c r="X10" s="4">
         <v>0</v>
       </c>
-      <c r="Y10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4">
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:31">
+    <row r="11" customHeight="1" spans="1:30">
       <c r="A11" s="3">
         <v>2002</v>
       </c>
@@ -2200,10 +2179,10 @@
         <v>2002</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2212,71 +2191,65 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="K11" s="4">
+        <v>5</v>
       </c>
       <c r="L11" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M11" s="4">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="N11" s="4">
         <v>1.5</v>
       </c>
-      <c r="O11" s="4">
-        <v>35</v>
+      <c r="O11" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="R11" s="4">
+        <v>97</v>
+      </c>
+      <c r="Q11" s="4">
         <v>5</v>
       </c>
-      <c r="S11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="U11" s="4">
+      <c r="R11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="T11" s="4">
         <v>150</v>
       </c>
-      <c r="V11" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="W11" s="4">
+      <c r="U11" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="V11" s="4">
         <v>40</v>
       </c>
       <c r="X11" s="4">
         <v>0</v>
       </c>
-      <c r="Y11" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4">
+      <c r="Y11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:31">
+    <row r="12" customHeight="1" spans="1:30">
       <c r="A12" s="3">
         <v>2003</v>
       </c>
@@ -2287,10 +2260,10 @@
         <v>2003</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2299,58 +2272,55 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
+      </c>
+      <c r="K12" s="4">
+        <v>5</v>
       </c>
       <c r="L12" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M12" s="4">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="N12" s="4">
         <v>1.5</v>
       </c>
-      <c r="O12" s="4">
-        <v>35</v>
+      <c r="O12" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R12" s="4">
+        <v>80</v>
+      </c>
+      <c r="Q12" s="4">
         <v>10</v>
       </c>
-      <c r="S12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U12" s="4">
-        <v>0</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="W12" s="4">
+      <c r="R12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" s="4">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="V12" s="4">
         <v>0</v>
       </c>
       <c r="X12" s="4">
         <v>0</v>
       </c>
-      <c r="Y12" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="4" t="s">
-        <v>101</v>
+      <c r="Y12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>0</v>
       </c>
       <c r="AB12" s="4">
         <v>0</v>
@@ -2361,11 +2331,8 @@
       <c r="AD12" s="4">
         <v>0</v>
       </c>
-      <c r="AE12" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" customHeight="1" spans="1:31">
+    <row r="13" customHeight="1" spans="1:30">
       <c r="A13" s="3">
         <v>10001</v>
       </c>
@@ -2376,10 +2343,10 @@
         <v>10001</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2388,66 +2355,60 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="K13" s="4">
+        <v>2</v>
       </c>
       <c r="L13" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" s="4">
         <v>0</v>
       </c>
-      <c r="O13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R13" s="4">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="U13" s="4">
-        <v>0</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="W13" s="4">
+      <c r="P13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="V13" s="4">
         <v>0</v>
       </c>
       <c r="X13" s="4">
         <v>0.85</v>
       </c>
-      <c r="Y13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>107</v>
+      <c r="Y13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>50</v>
       </c>
       <c r="AB13" s="4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" s="4">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="4">
         <v>0</v>
       </c>
     </row>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -224,7 +224,7 @@
     <t>剑士基础连招一</t>
   </si>
   <si>
-    <t>Normal</t>
+    <t>Combo</t>
   </si>
   <si>
     <t>None</t>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -50,7 +50,7 @@
     <t>MaxLevel</t>
   </si>
   <si>
-    <t>Type</t>
+    <t>Mode</t>
   </si>
   <si>
     <t>Icon</t>
@@ -152,7 +152,7 @@
     <t>技能上限</t>
   </si>
   <si>
-    <t>类别</t>
+    <t>模式</t>
   </si>
   <si>
     <t>技能图标</t>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -263,7 +263,7 @@
     <t>Skill</t>
   </si>
   <si>
-    <t>Icons/skill_icon_04</t>
+    <t>Warriorskill_13</t>
   </si>
   <si>
     <t>Unit</t>
@@ -284,7 +284,7 @@
     <t>对单个目标造成物理攻击，添加流血效果</t>
   </si>
   <si>
-    <t>Icons/skill_icon_02</t>
+    <t>Warriorskill_10</t>
   </si>
   <si>
     <t>[0.3,0.6,0.9]</t>
@@ -299,7 +299,7 @@
     <t>对自身周围造成范围伤害</t>
   </si>
   <si>
-    <t>Icons/skill_icon_03</t>
+    <t>Warriorskill_35</t>
   </si>
   <si>
     <t>Spell</t>
@@ -317,9 +317,6 @@
     <t>法师的基础法术，无消耗</t>
   </si>
   <si>
-    <t>Icons/skill_icon_01</t>
-  </si>
-  <si>
     <t>Intonate</t>
   </si>
   <si>
@@ -330,9 +327,6 @@
   </si>
   <si>
     <t>对目标位置造成范围法术伤害</t>
-  </si>
-  <si>
-    <t>Icons/stoune_icon</t>
   </si>
   <si>
     <t>Effects/Fly/FireBall</t>
@@ -2121,9 +2115,6 @@
       <c r="H10" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="J10" s="4" t="s">
         <v>79</v>
       </c>
@@ -2140,22 +2131,22 @@
         <v>0.9</v>
       </c>
       <c r="O10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="V10" s="4">
         <v>0</v>
@@ -2179,10 +2170,10 @@
         <v>2002</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2193,9 +2184,6 @@
       <c r="H11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="J11" s="4" t="s">
         <v>79</v>
       </c>
@@ -2212,10 +2200,10 @@
         <v>1.5</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="4">
         <v>5</v>
@@ -2224,13 +2212,13 @@
         <v>1</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T11" s="4">
         <v>150</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V11" s="4">
         <v>40</v>
@@ -2239,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AB11" s="4">
         <v>0</v>
@@ -2260,10 +2248,10 @@
         <v>2003</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2274,11 +2262,8 @@
       <c r="H12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="J12" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2317,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AA12" s="4">
         <v>0</v>
@@ -2343,10 +2328,10 @@
         <v>10001</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2357,9 +2342,6 @@
       <c r="H13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="J13" s="4" t="s">
         <v>79</v>
       </c>
@@ -2388,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V13" s="4">
         <v>0</v>
@@ -2397,7 +2379,7 @@
         <v>0.85</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AA13" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -272,10 +272,10 @@
     <t>Attack</t>
   </si>
   <si>
+    <t>JianHengJi</t>
+  </si>
+  <si>
     <t>Effects/Hits/Holy hit</t>
-  </si>
-  <si>
-    <t>[0.4]</t>
   </si>
   <si>
     <t>剑刃噬心</t>
@@ -1885,7 +1885,7 @@
         <v>80</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q7" s="4">
         <v>0</v>
@@ -1897,16 +1897,16 @@
         <v>0</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V7" s="4">
         <v>0</v>
       </c>
       <c r="X7" s="4">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="AA7" s="4">
         <v>20</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V8" s="4">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V9" s="4">
         <v>40</v>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V12" s="4">
         <v>0</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -266,55 +266,55 @@
     <t>Warriorskill_13</t>
   </si>
   <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>JianHengJi</t>
+  </si>
+  <si>
+    <t>Effects/Hits/Holy hit</t>
+  </si>
+  <si>
+    <t>剑刃噬心</t>
+  </si>
+  <si>
+    <t>对单个目标造成物理攻击，添加流血效果</t>
+  </si>
+  <si>
+    <t>Warriorskill_10</t>
+  </si>
+  <si>
+    <t>[0.3,0.6,0.9]</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>剑荡八荒</t>
+  </si>
+  <si>
+    <t>对自身周围造成范围伤害</t>
+  </si>
+  <si>
+    <t>Warriorskill_35</t>
+  </si>
+  <si>
+    <t>Spell</t>
+  </si>
+  <si>
+    <t>Attack04_Spinning_SwordAndShield</t>
+  </si>
+  <si>
+    <t>[0.4,0.8,1.2]</t>
+  </si>
+  <si>
+    <t>火灵咒</t>
+  </si>
+  <si>
+    <t>法师的基础法术，无消耗</t>
+  </si>
+  <si>
     <t>Unit</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>JianHengJi</t>
-  </si>
-  <si>
-    <t>Effects/Hits/Holy hit</t>
-  </si>
-  <si>
-    <t>剑刃噬心</t>
-  </si>
-  <si>
-    <t>对单个目标造成物理攻击，添加流血效果</t>
-  </si>
-  <si>
-    <t>Warriorskill_10</t>
-  </si>
-  <si>
-    <t>[0.3,0.6,0.9]</t>
-  </si>
-  <si>
-    <t>[1]</t>
-  </si>
-  <si>
-    <t>剑荡八荒</t>
-  </si>
-  <si>
-    <t>对自身周围造成范围伤害</t>
-  </si>
-  <si>
-    <t>Warriorskill_35</t>
-  </si>
-  <si>
-    <t>Spell</t>
-  </si>
-  <si>
-    <t>Attack04_Spinning_SwordAndShield</t>
-  </si>
-  <si>
-    <t>[0.4,0.8,1.2]</t>
-  </si>
-  <si>
-    <t>火灵咒</t>
-  </si>
-  <si>
-    <t>法师的基础法术，无消耗</t>
   </si>
   <si>
     <t>Intonate</t>
@@ -1867,7 +1867,7 @@
         <v>78</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="K7" s="4">
         <v>1.5</v>
@@ -1882,22 +1882,22 @@
         <v>0</v>
       </c>
       <c r="O7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="V7" s="4">
         <v>0</v>
@@ -1932,10 +1932,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1947,10 +1947,10 @@
         <v>77</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="K8" s="4">
         <v>5</v>
@@ -1965,22 +1965,22 @@
         <v>0</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
       </c>
       <c r="R8" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" s="4">
         <v>0</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V8" s="4">
         <v>0</v>
@@ -1989,10 +1989,10 @@
         <v>0.85</v>
       </c>
       <c r="Y8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z8" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="Z8" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="AA8" s="4">
         <v>40</v>
@@ -2018,10 +2018,10 @@
         <v>1003</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -2033,7 +2033,7 @@
         <v>77</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>66</v>
@@ -2051,22 +2051,22 @@
         <v>0</v>
       </c>
       <c r="O9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
       </c>
       <c r="R9" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" s="4">
         <v>0</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V9" s="4">
         <v>40</v>
@@ -2075,7 +2075,7 @@
         <v>1.5</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA9" s="4">
         <v>60</v>
@@ -2101,10 +2101,10 @@
         <v>2001</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2116,7 +2116,7 @@
         <v>77</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K10" s="4">
         <v>1.5</v>
@@ -2185,7 +2185,7 @@
         <v>77</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K11" s="4">
         <v>5</v>
@@ -2278,10 +2278,10 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q12" s="4">
         <v>10</v>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V12" s="4">
         <v>0</v>
@@ -2343,7 +2343,7 @@
         <v>77</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K13" s="4">
         <v>2</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q13" s="4">
         <v>0</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="111">
   <si>
     <t>ID</t>
   </si>
@@ -266,79 +266,88 @@
     <t>Warriorskill_13</t>
   </si>
   <si>
+    <t>JianHengJi</t>
+  </si>
+  <si>
+    <t>Effects/Hits/Holy hit</t>
+  </si>
+  <si>
+    <t>龙牙猛击</t>
+  </si>
+  <si>
+    <t>对穿刺范围内的目标造成物理攻击，添加流血效果</t>
+  </si>
+  <si>
+    <t>Archerskill_05</t>
+  </si>
+  <si>
+    <t>LongYaMengJi</t>
+  </si>
+  <si>
+    <t>[0.3,0.6,0.9]</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>剑刃噬心</t>
+  </si>
+  <si>
+    <t>对自身周围造成范围伤害</t>
+  </si>
+  <si>
+    <t>Warriorskill_35</t>
+  </si>
+  <si>
+    <t>JianRenShiXin</t>
+  </si>
+  <si>
+    <t>[0.4,0.8,1.2]</t>
+  </si>
+  <si>
+    <t>沉天陨击</t>
+  </si>
+  <si>
+    <t>Priestskill_28</t>
+  </si>
+  <si>
+    <t>ChenTianYunJi</t>
+  </si>
+  <si>
+    <t>火灵咒</t>
+  </si>
+  <si>
+    <t>法师的基础法术，无消耗</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Intonate</t>
+  </si>
+  <si>
+    <t>Effects/Hits/Explosion</t>
+  </si>
+  <si>
+    <t>南明离火</t>
+  </si>
+  <si>
+    <t>对目标位置造成范围法术伤害</t>
+  </si>
+  <si>
+    <t>Effects/Fly/FireBall</t>
+  </si>
+  <si>
+    <t>[0.2]</t>
+  </si>
+  <si>
+    <t>自定义技能</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
     <t>Attack</t>
-  </si>
-  <si>
-    <t>JianHengJi</t>
-  </si>
-  <si>
-    <t>Effects/Hits/Holy hit</t>
-  </si>
-  <si>
-    <t>剑刃噬心</t>
-  </si>
-  <si>
-    <t>对单个目标造成物理攻击，添加流血效果</t>
-  </si>
-  <si>
-    <t>Warriorskill_10</t>
-  </si>
-  <si>
-    <t>[0.3,0.6,0.9]</t>
-  </si>
-  <si>
-    <t>[1]</t>
-  </si>
-  <si>
-    <t>剑荡八荒</t>
-  </si>
-  <si>
-    <t>对自身周围造成范围伤害</t>
-  </si>
-  <si>
-    <t>Warriorskill_35</t>
-  </si>
-  <si>
-    <t>Spell</t>
-  </si>
-  <si>
-    <t>Attack04_Spinning_SwordAndShield</t>
-  </si>
-  <si>
-    <t>[0.4,0.8,1.2]</t>
-  </si>
-  <si>
-    <t>火灵咒</t>
-  </si>
-  <si>
-    <t>法师的基础法术，无消耗</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Intonate</t>
-  </si>
-  <si>
-    <t>Effects/Hits/Explosion</t>
-  </si>
-  <si>
-    <t>南明离火</t>
-  </si>
-  <si>
-    <t>对目标位置造成范围法术伤害</t>
-  </si>
-  <si>
-    <t>Effects/Fly/FireBall</t>
-  </si>
-  <si>
-    <t>[0.2]</t>
-  </si>
-  <si>
-    <t>自定义技能</t>
-  </si>
-  <si>
-    <t>Position</t>
   </si>
   <si>
     <t>野怪近战[物理]</t>
@@ -1320,7 +1329,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1881,23 +1890,21 @@
       <c r="N7" s="4">
         <v>0</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="4"/>
+      <c r="P7" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="V7" s="4">
         <v>0</v>
@@ -1932,10 +1939,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1947,13 +1954,13 @@
         <v>77</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>66</v>
       </c>
       <c r="K8" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L8" s="4">
         <v>3.5</v>
@@ -1964,11 +1971,9 @@
       <c r="N8" s="4">
         <v>0</v>
       </c>
-      <c r="O8" s="4" t="s">
-        <v>79</v>
-      </c>
+      <c r="O8" s="4"/>
       <c r="P8" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
@@ -1980,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V8" s="4">
         <v>0</v>
@@ -2039,7 +2044,7 @@
         <v>66</v>
       </c>
       <c r="K9" s="4">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="L9" s="4">
         <v>0</v>
@@ -2050,11 +2055,9 @@
       <c r="N9" s="4">
         <v>0</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="4"/>
+      <c r="P9" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2066,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V9" s="4">
         <v>40</v>
@@ -2075,7 +2078,7 @@
         <v>1.5</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AA9" s="4">
         <v>60</v>
@@ -2092,19 +2095,19 @@
     </row>
     <row r="10" customHeight="1" spans="1:30">
       <c r="A10" s="3">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="B10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3">
-        <v>2001</v>
+        <v>1004</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2115,65 +2118,77 @@
       <c r="H10" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="I10" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="J10" s="4" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K10" s="4">
+        <v>10</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4">
+        <v>25</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>10</v>
+      </c>
+      <c r="R10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="V10" s="4">
+        <v>40</v>
+      </c>
+      <c r="X10" s="4">
         <v>1.5</v>
       </c>
-      <c r="L10" s="4">
-        <v>10</v>
-      </c>
-      <c r="M10" s="4">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="V10" s="4">
-        <v>0</v>
-      </c>
-      <c r="X10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="4"/>
+      <c r="Y10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>60</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>0.8</v>
+      </c>
       <c r="AD10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:30">
       <c r="A11" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
       </c>
       <c r="C11" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2185,51 +2200,42 @@
         <v>77</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K11" s="4">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M11" s="4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q11" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="S11" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="T11" s="4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="V11" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X11" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB11" s="4">
         <v>0</v>
       </c>
       <c r="AC11" s="4"/>
@@ -2239,19 +2245,19 @@
     </row>
     <row r="12" customHeight="1" spans="1:30">
       <c r="A12" s="3">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
       </c>
       <c r="C12" s="3">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2263,13 +2269,13 @@
         <v>77</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
       </c>
       <c r="L12" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M12" s="4">
         <v>35</v>
@@ -2278,60 +2284,58 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="Q12" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R12" s="4" t="b">
         <v>1</v>
       </c>
+      <c r="S12" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="T12" s="4">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="V12" s="4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X12" s="4">
         <v>0</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA12" s="4">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AB12" s="4">
         <v>0</v>
       </c>
-      <c r="AC12" s="4">
-        <v>0</v>
-      </c>
+      <c r="AC12" s="4"/>
       <c r="AD12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:30">
       <c r="A13" s="3">
-        <v>10001</v>
+        <v>2003</v>
       </c>
       <c r="B13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" s="3">
-        <v>10001</v>
+        <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>104</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2343,54 +2347,134 @@
         <v>77</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K13" s="4">
+        <v>5</v>
+      </c>
+      <c r="L13" s="4">
+        <v>10</v>
+      </c>
+      <c r="M13" s="4">
+        <v>35</v>
+      </c>
+      <c r="N13" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>10</v>
+      </c>
+      <c r="R13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="V13" s="4">
+        <v>0</v>
+      </c>
+      <c r="X13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:30">
+      <c r="A14" s="3">
+        <v>10001</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>10001</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" s="4">
         <v>2</v>
       </c>
-      <c r="L13" s="4">
+      <c r="L14" s="4">
         <v>3</v>
       </c>
-      <c r="M13" s="4">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T13" s="4">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4" t="s">
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="V13" s="4">
-        <v>0</v>
-      </c>
-      <c r="X13" s="4">
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" s="4">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="V14" s="4">
+        <v>0</v>
+      </c>
+      <c r="X14" s="4">
         <v>0.85</v>
       </c>
-      <c r="Y13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA13" s="4">
+      <c r="Y14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA14" s="4">
         <v>50</v>
       </c>
-      <c r="AB13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="4">
+      <c r="AB14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="4">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="4">
         <v>0</v>
       </c>
     </row>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,30 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
+    <workbookView windowWidth="22700" windowHeight="6630" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="105">
   <si>
     <t>ID</t>
   </si>
@@ -80,13 +67,7 @@
     <t>ReqLevel</t>
   </si>
   <si>
-    <t>IsMissile</t>
-  </si>
-  <si>
-    <t>Missile</t>
-  </si>
-  <si>
-    <t>MissileSpeed</t>
+    <t>MissileUnitId</t>
   </si>
   <si>
     <t>HitArt</t>
@@ -128,9 +109,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>编号</t>
   </si>
   <si>
@@ -182,13 +160,7 @@
     <t>等级要求</t>
   </si>
   <si>
-    <t>是否投射物</t>
-  </si>
-  <si>
-    <t>投射物</t>
-  </si>
-  <si>
-    <t>投射速度</t>
+    <t>投射物UnitId</t>
   </si>
   <si>
     <t>击中效果</t>
@@ -333,9 +305,6 @@
   </si>
   <si>
     <t>对目标位置造成范围法术伤害</t>
-  </si>
-  <si>
-    <t>Effects/Fly/FireBall</t>
   </si>
   <si>
     <t>[0.2]</t>
@@ -365,7 +334,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -389,6 +358,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -402,6 +399,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -441,21 +446,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -506,28 +496,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -548,13 +517,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,24 +583,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -608,18 +625,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -632,36 +637,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -680,19 +661,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,6 +710,21 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -774,21 +758,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -845,148 +814,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1013,52 +982,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1329,7 +1298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1345,20 +1314,19 @@
     <col min="14" max="14" width="15.75" style="4" customWidth="1"/>
     <col min="15" max="15" width="12.875" style="4" customWidth="1"/>
     <col min="16" max="16" width="31.125" style="4" customWidth="1"/>
-    <col min="17" max="18" width="10.875" style="4" customWidth="1"/>
-    <col min="19" max="19" width="25.25" style="4" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="4" customWidth="1"/>
-    <col min="21" max="21" width="35.75" style="4" customWidth="1"/>
-    <col min="22" max="22" width="9.625" style="4" customWidth="1"/>
-    <col min="23" max="24" width="10.25" style="4" customWidth="1"/>
-    <col min="25" max="25" width="18.125" style="4" customWidth="1"/>
-    <col min="26" max="26" width="9" style="4" customWidth="1"/>
-    <col min="27" max="28" width="9" style="4"/>
-    <col min="29" max="29" width="12" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="4"/>
+    <col min="17" max="17" width="10.875" style="4" customWidth="1"/>
+    <col min="18" max="18" width="25.25" style="4" customWidth="1"/>
+    <col min="19" max="19" width="35.75" style="4" customWidth="1"/>
+    <col min="20" max="20" width="9.625" style="4" customWidth="1"/>
+    <col min="21" max="22" width="10.25" style="4" customWidth="1"/>
+    <col min="23" max="23" width="18.125" style="4" customWidth="1"/>
+    <col min="24" max="24" width="9" style="4" customWidth="1"/>
+    <col min="25" max="26" width="9" style="4"/>
+    <col min="27" max="27" width="12" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:30">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1443,198 +1411,180 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:30">
-      <c r="A2" s="5" t="s">
+      <c r="E2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="L2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="M2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>32</v>
+      <c r="C3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:30">
-      <c r="A3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:30">
+    <row r="4" customHeight="1" spans="1:28">
       <c r="A4" s="3">
         <v>101</v>
       </c>
@@ -1645,7 +1595,7 @@
         <v>101</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -1654,10 +1604,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="K4" s="4">
         <v>0</v>
@@ -1674,38 +1624,35 @@
       <c r="Q4" s="4">
         <v>0</v>
       </c>
-      <c r="R4" s="4" t="b">
+      <c r="R4" s="4">
         <v>0</v>
       </c>
       <c r="T4" s="4">
-        <v>0</v>
+        <v>1.7</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="V4" s="4">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="X4" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>0</v>
       </c>
       <c r="AA4" s="4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AB4" s="4">
         <v>0</v>
       </c>
-      <c r="AC4" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="AD4" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" customHeight="1" spans="1:30">
+    <row r="5" customHeight="1" spans="1:28">
       <c r="A5" s="3">
         <v>102</v>
       </c>
@@ -1716,7 +1663,7 @@
         <v>102</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -1725,58 +1672,55 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="U5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="V5" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="W5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4">
-        <v>1.8</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="X5" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>71</v>
+      <c r="Y5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>0</v>
       </c>
       <c r="AA5" s="4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AB5" s="4">
         <v>0</v>
       </c>
-      <c r="AC5" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="AD5" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" customHeight="1" spans="1:30">
+    <row r="6" customHeight="1" spans="1:28">
       <c r="A6" s="3">
         <v>103</v>
       </c>
@@ -1787,7 +1731,7 @@
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1796,10 +1740,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="K6" s="4">
         <v>0</v>
@@ -1816,38 +1760,35 @@
       <c r="Q6" s="4">
         <v>0</v>
       </c>
-      <c r="R6" s="4" t="b">
+      <c r="R6" s="4">
         <v>0</v>
       </c>
       <c r="T6" s="4">
-        <v>0</v>
+        <v>2.5</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="V6" s="4">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="X6" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>0</v>
       </c>
       <c r="AA6" s="4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB6" s="4">
         <v>0</v>
       </c>
-      <c r="AC6" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="AD6" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" customHeight="1" spans="1:30">
+    <row r="7" customHeight="1" spans="1:28">
       <c r="A7" s="3">
         <v>1001</v>
       </c>
@@ -1858,10 +1799,10 @@
         <v>1001</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1870,13 +1811,13 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="K7" s="4">
         <v>1.5</v>
@@ -1890,45 +1831,41 @@
       <c r="N7" s="4">
         <v>0</v>
       </c>
-      <c r="O7" s="4"/>
       <c r="P7" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Q7" s="4">
         <v>0</v>
       </c>
-      <c r="R7" s="4" t="b">
-        <v>0</v>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="T7" s="4">
         <v>0</v>
       </c>
-      <c r="U7" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="V7" s="4">
-        <v>0</v>
-      </c>
-      <c r="X7" s="4">
         <v>0.4</v>
       </c>
-      <c r="Y7" s="4" t="s">
-        <v>68</v>
+      <c r="W7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>20</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>0</v>
       </c>
       <c r="AA7" s="4">
-        <v>20</v>
+        <v>0.8</v>
       </c>
       <c r="AB7" s="4">
         <v>0</v>
       </c>
-      <c r="AC7" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="AD7" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" customHeight="1" spans="1:30">
+    <row r="8" customHeight="1" spans="1:28">
       <c r="A8" s="3">
         <v>1002</v>
       </c>
@@ -1939,10 +1876,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1951,13 +1888,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="K8" s="4">
         <v>3</v>
@@ -1971,48 +1908,44 @@
       <c r="N8" s="4">
         <v>0</v>
       </c>
-      <c r="O8" s="4"/>
       <c r="P8" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
       </c>
-      <c r="R8" s="4" t="b">
-        <v>0</v>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="T8" s="4">
         <v>0</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="V8" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="W8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="V8" s="4">
-        <v>0</v>
-      </c>
-      <c r="X8" s="4">
-        <v>0.85</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z8" s="4" t="s">
-        <v>86</v>
+      <c r="X8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>40</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>0</v>
       </c>
       <c r="AA8" s="4">
-        <v>40</v>
+        <v>0.6</v>
       </c>
       <c r="AB8" s="4">
         <v>0</v>
       </c>
-      <c r="AC8" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="AD8" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" customHeight="1" spans="1:30">
+    <row r="9" customHeight="1" spans="1:28">
       <c r="A9" s="3">
         <v>1003</v>
       </c>
@@ -2023,10 +1956,10 @@
         <v>1003</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -2035,13 +1968,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="K9" s="4">
         <v>7</v>
@@ -2055,45 +1988,41 @@
       <c r="N9" s="4">
         <v>0</v>
       </c>
-      <c r="O9" s="4"/>
       <c r="P9" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
       </c>
-      <c r="R9" s="4" t="b">
-        <v>0</v>
+      <c r="R9" s="4">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V9" s="4">
-        <v>40</v>
-      </c>
-      <c r="X9" s="4">
         <v>1.5</v>
       </c>
-      <c r="Y9" s="4" t="s">
-        <v>91</v>
+      <c r="W9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>60</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>0</v>
       </c>
       <c r="AA9" s="4">
-        <v>60</v>
+        <v>0.8</v>
       </c>
       <c r="AB9" s="4">
         <v>0</v>
       </c>
-      <c r="AC9" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="AD9" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" customHeight="1" spans="1:30">
+    <row r="10" customHeight="1" spans="1:28">
       <c r="A10" s="3">
         <v>1004</v>
       </c>
@@ -2104,25 +2033,25 @@
         <v>1004</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="J10" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="K10" s="4">
         <v>10</v>
@@ -2136,45 +2065,41 @@
       <c r="N10" s="4">
         <v>0</v>
       </c>
-      <c r="O10" s="4"/>
       <c r="P10" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="Q10" s="4">
         <v>10</v>
       </c>
-      <c r="R10" s="4" t="b">
-        <v>0</v>
+      <c r="R10" s="4">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="V10" s="4">
-        <v>40</v>
-      </c>
-      <c r="X10" s="4">
         <v>1.5</v>
       </c>
-      <c r="Y10" s="4" t="s">
-        <v>91</v>
+      <c r="W10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>60</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>0</v>
       </c>
       <c r="AA10" s="4">
-        <v>60</v>
+        <v>0.8</v>
       </c>
       <c r="AB10" s="4">
         <v>0</v>
       </c>
-      <c r="AC10" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="AD10" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" customHeight="1" spans="1:30">
+    <row r="11" customHeight="1" spans="1:28">
       <c r="A11" s="3">
         <v>2001</v>
       </c>
@@ -2185,10 +2110,10 @@
         <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2197,10 +2122,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K11" s="4">
         <v>1.5</v>
@@ -2215,35 +2140,32 @@
         <v>0.9</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="4">
         <v>0</v>
       </c>
-      <c r="R11" s="4" t="b">
-        <v>1</v>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="T11" s="4">
         <v>0</v>
       </c>
-      <c r="U11" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="V11" s="4">
         <v>0</v>
       </c>
-      <c r="X11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="4"/>
-      <c r="AD11" s="4">
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:30">
+    <row r="12" customHeight="1" spans="1:28">
       <c r="A12" s="3">
         <v>2002</v>
       </c>
@@ -2254,10 +2176,10 @@
         <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2266,10 +2188,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2284,44 +2206,38 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="Q12" s="4">
         <v>5</v>
       </c>
-      <c r="R12" s="4" t="b">
-        <v>1</v>
+      <c r="R12" s="4">
+        <v>0</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T12" s="4">
-        <v>150</v>
-      </c>
-      <c r="U12" s="4" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="V12" s="4">
-        <v>40</v>
-      </c>
-      <c r="X12" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="4" t="s">
-        <v>103</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="4"/>
       <c r="AB12" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:30">
+    <row r="13" customHeight="1" spans="1:28">
       <c r="A13" s="3">
         <v>2003</v>
       </c>
@@ -2332,10 +2248,10 @@
         <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2344,10 +2260,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
@@ -2362,31 +2278,34 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="Q13" s="4">
         <v>10</v>
       </c>
-      <c r="R13" s="4" t="b">
-        <v>1</v>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="T13" s="4">
         <v>0</v>
       </c>
-      <c r="U13" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="V13" s="4">
         <v>0</v>
       </c>
-      <c r="X13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>103</v>
+      <c r="W13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>0</v>
       </c>
       <c r="AA13" s="4">
         <v>0</v>
@@ -2394,14 +2313,8 @@
       <c r="AB13" s="4">
         <v>0</v>
       </c>
-      <c r="AC13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" customHeight="1" spans="1:30">
+    <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="3">
         <v>10001</v>
       </c>
@@ -2412,10 +2325,10 @@
         <v>10001</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -2424,10 +2337,10 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K14" s="4">
         <v>2</v>
@@ -2442,39 +2355,36 @@
         <v>0</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="4">
         <v>0</v>
       </c>
-      <c r="R14" s="4" t="b">
-        <v>1</v>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="T14" s="4">
         <v>0</v>
       </c>
-      <c r="U14" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="V14" s="4">
-        <v>0</v>
-      </c>
-      <c r="X14" s="4">
         <v>0.85</v>
       </c>
-      <c r="Y14" s="4" t="s">
-        <v>110</v>
+      <c r="W14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>50</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>0</v>
       </c>
       <c r="AA14" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="AB14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="4">
         <v>0</v>
       </c>
     </row>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22700" windowHeight="6630" tabRatio="173"/>
+    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="107">
   <si>
     <t>ID</t>
   </si>
@@ -244,6 +257,9 @@
     <t>Effects/Hits/Holy hit</t>
   </si>
   <si>
+    <t>(0,0,1)</t>
+  </si>
+  <si>
     <t>龙牙猛击</t>
   </si>
   <si>
@@ -256,7 +272,10 @@
     <t>LongYaMengJi</t>
   </si>
   <si>
-    <t>[0.3,0.6,0.9]</t>
+    <t>(0,1.1,2.45)</t>
+  </si>
+  <si>
+    <t>[0.6]</t>
   </si>
   <si>
     <t>[1]</t>
@@ -274,9 +293,6 @@
     <t>JianRenShiXin</t>
   </si>
   <si>
-    <t>[0.4,0.8,1.2]</t>
-  </si>
-  <si>
     <t>沉天陨击</t>
   </si>
   <si>
@@ -286,6 +302,12 @@
     <t>ChenTianYunJi</t>
   </si>
   <si>
+    <t>(0,0,1.5)</t>
+  </si>
+  <si>
+    <t>[0.5]</t>
+  </si>
+  <si>
     <t>火灵咒</t>
   </si>
   <si>
@@ -326,15 +348,12 @@
   </si>
   <si>
     <t>Effects/Hits/Stones hit</t>
-  </si>
-  <si>
-    <t>[0.5]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -358,34 +377,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -399,14 +390,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -446,6 +429,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -496,7 +494,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,49 +536,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,97 +674,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,21 +729,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -758,6 +762,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -814,148 +833,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -982,52 +1001,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1315,8 +1334,8 @@
     <col min="15" max="15" width="12.875" style="4" customWidth="1"/>
     <col min="16" max="16" width="31.125" style="4" customWidth="1"/>
     <col min="17" max="17" width="10.875" style="4" customWidth="1"/>
-    <col min="18" max="18" width="25.25" style="4" customWidth="1"/>
-    <col min="19" max="19" width="35.75" style="4" customWidth="1"/>
+    <col min="18" max="18" width="16.4666666666667" style="4" customWidth="1"/>
+    <col min="19" max="19" width="25.575" style="4" customWidth="1"/>
     <col min="20" max="20" width="9.625" style="4" customWidth="1"/>
     <col min="21" max="22" width="10.25" style="4" customWidth="1"/>
     <col min="23" max="23" width="18.125" style="4" customWidth="1"/>
@@ -1844,7 +1863,10 @@
         <v>75</v>
       </c>
       <c r="T7" s="4">
-        <v>0</v>
+        <v>4.5</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="V7" s="4">
         <v>0.4</v>
@@ -1876,10 +1898,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1891,7 +1913,7 @@
         <v>72</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>61</v>
@@ -1909,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
@@ -1921,16 +1943,19 @@
         <v>75</v>
       </c>
       <c r="T8" s="4">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="V8" s="4">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Y8" s="4">
         <v>40</v>
@@ -1956,10 +1981,10 @@
         <v>1003</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -1971,7 +1996,7 @@
         <v>72</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>61</v>
@@ -1989,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2000,15 +2025,7 @@
       <c r="S9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="T9" s="4">
-        <v>40</v>
-      </c>
-      <c r="V9" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>86</v>
-      </c>
+      <c r="T9" s="4"/>
       <c r="Y9" s="4">
         <v>60</v>
       </c>
@@ -2033,10 +2050,10 @@
         <v>1004</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2048,7 +2065,7 @@
         <v>72</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>61</v>
@@ -2066,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q10" s="4">
         <v>10</v>
@@ -2078,13 +2095,16 @@
         <v>75</v>
       </c>
       <c r="T10" s="4">
-        <v>40</v>
+        <v>7</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="V10" s="4">
         <v>1.5</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="Y10" s="4">
         <v>60</v>
@@ -2110,10 +2130,10 @@
         <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2125,7 +2145,7 @@
         <v>72</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K11" s="4">
         <v>1.5</v>
@@ -2140,10 +2160,10 @@
         <v>0.9</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="4">
         <v>0</v>
@@ -2152,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="T11" s="4">
         <v>0</v>
@@ -2176,10 +2196,10 @@
         <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2191,7 +2211,7 @@
         <v>72</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2206,10 +2226,10 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q12" s="4">
         <v>5</v>
@@ -2218,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="T12" s="4">
         <v>40</v>
@@ -2227,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Z12" s="4">
         <v>0</v>
@@ -2248,10 +2268,10 @@
         <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2263,7 +2283,7 @@
         <v>72</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
@@ -2278,10 +2298,10 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q13" s="4">
         <v>10</v>
@@ -2299,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y13" s="4">
         <v>0</v>
@@ -2325,10 +2345,10 @@
         <v>10001</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -2340,7 +2360,7 @@
         <v>72</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K14" s="4">
         <v>2</v>
@@ -2355,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q14" s="4">
         <v>0</v>
@@ -2364,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="T14" s="4">
         <v>0</v>
@@ -2373,7 +2393,7 @@
         <v>0.85</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="Y14" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -215,7 +215,7 @@
     <t>None</t>
   </si>
   <si>
-    <t>(0,1.2,1)</t>
+    <t>(0,1.2,2)</t>
   </si>
   <si>
     <t>[0.3]</t>
@@ -224,19 +224,7 @@
     <t>剑士基础连招二</t>
   </si>
   <si>
-    <t>(0,1.3,0.3)</t>
-  </si>
-  <si>
-    <t>[0.1]</t>
-  </si>
-  <si>
     <t>剑士基础连招三</t>
-  </si>
-  <si>
-    <t>(0,1.7,0.4)</t>
-  </si>
-  <si>
-    <t>[0.7]</t>
   </si>
   <si>
     <t>横剑击</t>
@@ -1647,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="4">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="U4" s="4" t="s">
         <v>62</v>
@@ -1659,7 +1647,7 @@
         <v>63</v>
       </c>
       <c r="Y4" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z4" s="4">
         <v>0</v>
@@ -1715,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="T5" s="4">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="V5" s="4">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="Y5" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z5" s="4">
         <v>0</v>
@@ -1750,7 +1738,7 @@
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1783,19 +1771,19 @@
         <v>0</v>
       </c>
       <c r="T6" s="4">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="V6" s="4">
         <v>0.4</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="Y6" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z6" s="4">
         <v>0</v>
@@ -1818,10 +1806,10 @@
         <v>1001</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1830,10 +1818,10 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>61</v>
@@ -1851,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q7" s="4">
         <v>0</v>
@@ -1860,13 +1848,13 @@
         <v>0</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="T7" s="4">
         <v>4.5</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="V7" s="4">
         <v>0.4</v>
@@ -1898,10 +1886,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1910,10 +1898,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>61</v>
@@ -1931,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
@@ -1940,22 +1928,22 @@
         <v>0</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="T8" s="4">
         <v>3</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="V8" s="4">
         <v>0.3</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="Y8" s="4">
         <v>40</v>
@@ -1981,10 +1969,10 @@
         <v>1003</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -1993,10 +1981,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>61</v>
@@ -2014,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2023,9 +2011,8 @@
         <v>0</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="T9" s="4"/>
+        <v>71</v>
+      </c>
       <c r="Y9" s="4">
         <v>60</v>
       </c>
@@ -2050,22 +2037,22 @@
         <v>1004</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>61</v>
@@ -2083,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q10" s="4">
         <v>10</v>
@@ -2092,19 +2079,19 @@
         <v>0</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="T10" s="4">
         <v>7</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="V10" s="4">
         <v>1.5</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Y10" s="4">
         <v>60</v>
@@ -2130,10 +2117,10 @@
         <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2142,10 +2129,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K11" s="4">
         <v>1.5</v>
@@ -2160,10 +2147,10 @@
         <v>0.9</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Q11" s="4">
         <v>0</v>
@@ -2172,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="T11" s="4">
         <v>0</v>
@@ -2196,10 +2183,10 @@
         <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2208,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2226,10 +2213,10 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Q12" s="4">
         <v>5</v>
@@ -2238,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="T12" s="4">
         <v>40</v>
@@ -2247,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Z12" s="4">
         <v>0</v>
@@ -2268,10 +2255,10 @@
         <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2280,10 +2267,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
@@ -2298,10 +2285,10 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="Q13" s="4">
         <v>10</v>
@@ -2310,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="T13" s="4">
         <v>0</v>
@@ -2319,7 +2306,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Y13" s="4">
         <v>0</v>
@@ -2345,10 +2332,10 @@
         <v>10001</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -2357,10 +2344,10 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K14" s="4">
         <v>2</v>
@@ -2375,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="Q14" s="4">
         <v>0</v>
@@ -2384,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="T14" s="4">
         <v>0</v>
@@ -2393,7 +2380,7 @@
         <v>0.85</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Y14" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -86,15 +86,15 @@
     <t>HitArt</t>
   </si>
   <si>
+    <t>Duration</t>
+  </si>
+  <si>
     <t>Area</t>
   </si>
   <si>
     <t>AreaOffset</t>
   </si>
   <si>
-    <t>Duration</t>
-  </si>
-  <si>
     <t>HitDelay</t>
   </si>
   <si>
@@ -179,13 +179,13 @@
     <t>击中效果</t>
   </si>
   <si>
+    <t>持续时间</t>
+  </si>
+  <si>
     <t>影响区域</t>
   </si>
   <si>
     <t>区域偏移</t>
-  </si>
-  <si>
-    <t>持续时间</t>
   </si>
   <si>
     <t>命中延迟</t>
@@ -1324,8 +1324,9 @@
     <col min="17" max="17" width="10.875" style="4" customWidth="1"/>
     <col min="18" max="18" width="16.4666666666667" style="4" customWidth="1"/>
     <col min="19" max="19" width="25.575" style="4" customWidth="1"/>
-    <col min="20" max="20" width="9.625" style="4" customWidth="1"/>
-    <col min="21" max="22" width="10.25" style="4" customWidth="1"/>
+    <col min="20" max="20" width="10.25" style="4" customWidth="1"/>
+    <col min="21" max="21" width="9.625" style="4" customWidth="1"/>
+    <col min="22" max="22" width="10.25" style="4" customWidth="1"/>
     <col min="23" max="23" width="18.125" style="4" customWidth="1"/>
     <col min="24" max="24" width="9" style="4" customWidth="1"/>
     <col min="25" max="26" width="9" style="4"/>
@@ -1481,10 +1482,10 @@
         <v>30</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>29</v>
@@ -1635,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="T4" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="U4" s="4">
         <v>4.5</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="V4" s="4">
-        <v>0.4</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>63</v>
@@ -1703,13 +1704,13 @@
         <v>0</v>
       </c>
       <c r="T5" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="U5" s="4">
         <v>4.5</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="V5" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="V5" s="4">
-        <v>0.4</v>
       </c>
       <c r="W5" s="4" t="s">
         <v>63</v>
@@ -1771,13 +1772,13 @@
         <v>0</v>
       </c>
       <c r="T6" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="U6" s="4">
         <v>4.5</v>
       </c>
-      <c r="U6" s="4" t="s">
+      <c r="V6" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="V6" s="4">
-        <v>0.4</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>63</v>
@@ -1851,13 +1852,13 @@
         <v>71</v>
       </c>
       <c r="T7" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="U7" s="4">
         <v>4.5</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="V7" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="V7" s="4">
-        <v>0.4</v>
       </c>
       <c r="W7" s="4" t="s">
         <v>63</v>
@@ -1931,13 +1932,13 @@
         <v>71</v>
       </c>
       <c r="T8" s="4">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4">
         <v>3</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="V8" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="V8" s="4">
-        <v>0.3</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>78</v>
@@ -2013,6 +2014,9 @@
       <c r="S9" s="4" t="s">
         <v>71</v>
       </c>
+      <c r="T9" s="4">
+        <v>0.5</v>
+      </c>
       <c r="Y9" s="4">
         <v>60</v>
       </c>
@@ -2082,13 +2086,13 @@
         <v>71</v>
       </c>
       <c r="T10" s="4">
+        <v>2</v>
+      </c>
+      <c r="U10" s="4">
         <v>7</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="V10" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="V10" s="4">
-        <v>1.5</v>
       </c>
       <c r="W10" s="4" t="s">
         <v>88</v>
@@ -2164,7 +2168,7 @@
       <c r="T11" s="4">
         <v>0</v>
       </c>
-      <c r="V11" s="4">
+      <c r="U11" s="4">
         <v>0</v>
       </c>
       <c r="AA11" s="4"/>
@@ -2228,10 +2232,10 @@
         <v>93</v>
       </c>
       <c r="T12" s="4">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4">
         <v>40</v>
-      </c>
-      <c r="V12" s="4">
-        <v>0</v>
       </c>
       <c r="W12" s="4" t="s">
         <v>96</v>
@@ -2302,7 +2306,7 @@
       <c r="T13" s="4">
         <v>0</v>
       </c>
-      <c r="V13" s="4">
+      <c r="U13" s="4">
         <v>0</v>
       </c>
       <c r="W13" s="4" t="s">
@@ -2374,10 +2378,10 @@
         <v>102</v>
       </c>
       <c r="T14" s="4">
-        <v>0</v>
-      </c>
-      <c r="V14" s="4">
         <v>0.85</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
       </c>
       <c r="W14" s="4" t="s">
         <v>88</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,25 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
+    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -329,19 +316,19 @@
     <t>Attack</t>
   </si>
   <si>
-    <t>野怪近战[物理]</t>
-  </si>
-  <si>
-    <t>野怪通用近战物理攻击</t>
-  </si>
-  <si>
-    <t>Effects/Hits/Stones hit</t>
+    <t>哥布林近战</t>
+  </si>
+  <si>
+    <t>哥布林近战物理攻击</t>
+  </si>
+  <si>
+    <t>(0,0.2,2)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -365,6 +352,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -378,6 +393,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -417,21 +440,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -482,28 +490,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -524,13 +511,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,24 +577,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -584,18 +619,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -608,36 +631,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -656,19 +655,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -717,6 +704,21 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -750,21 +752,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -821,148 +808,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -989,52 +976,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -2330,7 +2317,7 @@
         <v>10001</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="C14" s="3">
         <v>10001</v>
@@ -2351,13 +2338,13 @@
         <v>68</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="K14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" s="4">
         <v>0</v>
@@ -2374,14 +2361,15 @@
       <c r="R14" s="4">
         <v>0</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="S14" s="4"/>
+      <c r="T14" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="U14" s="4">
+        <v>2</v>
+      </c>
+      <c r="V14" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="T14" s="4">
-        <v>0.85</v>
-      </c>
-      <c r="U14" s="4">
-        <v>0</v>
       </c>
       <c r="W14" s="4" t="s">
         <v>88</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
+    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="105">
   <si>
     <t>ID</t>
   </si>
@@ -100,6 +113,9 @@
     <t>Apc</t>
   </si>
   <si>
+    <t>Force</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -191,6 +207,9 @@
   </si>
   <si>
     <t>法攻加成</t>
+  </si>
+  <si>
+    <t>对实体施加的力</t>
   </si>
   <si>
     <t>剑士基础连招一</t>
@@ -328,7 +347,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -352,34 +371,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -393,14 +384,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -440,6 +423,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -490,7 +488,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -511,49 +530,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -565,97 +668,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -704,21 +723,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -752,6 +756,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -808,148 +827,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -976,52 +995,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1292,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1318,10 +1337,12 @@
     <col min="24" max="24" width="9" style="4" customWidth="1"/>
     <col min="25" max="26" width="9" style="4"/>
     <col min="27" max="27" width="12" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="4"/>
+    <col min="28" max="28" width="9" style="4"/>
+    <col min="29" max="29" width="13.45" style="4" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1406,180 +1427,189 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="H2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="T2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:29">
       <c r="A3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:28">
+    <row r="4" customHeight="1" spans="1:29">
       <c r="A4" s="3">
         <v>101</v>
       </c>
@@ -1590,7 +1620,7 @@
         <v>101</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -1599,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K4" s="4">
         <v>0</v>
@@ -1629,10 +1659,10 @@
         <v>4.5</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Y4" s="4">
         <v>100</v>
@@ -1646,8 +1676,11 @@
       <c r="AB4" s="4">
         <v>0</v>
       </c>
+      <c r="AC4" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="1:28">
+    <row r="5" customHeight="1" spans="1:29">
       <c r="A5" s="3">
         <v>102</v>
       </c>
@@ -1658,7 +1691,7 @@
         <v>102</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -1667,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K5" s="4">
         <v>0</v>
@@ -1697,10 +1730,10 @@
         <v>4.5</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Y5" s="4">
         <v>100</v>
@@ -1714,8 +1747,11 @@
       <c r="AB5" s="4">
         <v>0</v>
       </c>
+      <c r="AC5" s="4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" customHeight="1" spans="1:28">
+    <row r="6" customHeight="1" spans="1:29">
       <c r="A6" s="3">
         <v>103</v>
       </c>
@@ -1726,7 +1762,7 @@
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1735,10 +1771,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K6" s="4">
         <v>0</v>
@@ -1765,10 +1801,10 @@
         <v>4.5</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Y6" s="4">
         <v>100</v>
@@ -1781,6 +1817,9 @@
       </c>
       <c r="AB6" s="4">
         <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:28">
@@ -1794,10 +1833,10 @@
         <v>1001</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1806,13 +1845,13 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K7" s="4">
         <v>1.5</v>
@@ -1827,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="4">
         <v>0</v>
@@ -1836,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T7" s="4">
         <v>0.8</v>
@@ -1845,10 +1884,10 @@
         <v>4.5</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Y7" s="4">
         <v>20</v>
@@ -1874,10 +1913,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1886,13 +1925,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K8" s="4">
         <v>3</v>
@@ -1907,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
@@ -1916,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T8" s="4">
         <v>1</v>
@@ -1925,13 +1964,13 @@
         <v>3</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Y8" s="4">
         <v>40</v>
@@ -1957,10 +1996,10 @@
         <v>1003</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -1969,13 +2008,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K9" s="4">
         <v>7</v>
@@ -1990,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -1999,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T9" s="4">
         <v>0.5</v>
@@ -2028,10 +2067,10 @@
         <v>1004</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2040,13 +2079,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K10" s="4">
         <v>10</v>
@@ -2061,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q10" s="4">
         <v>10</v>
@@ -2070,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T10" s="4">
         <v>2</v>
@@ -2079,10 +2118,10 @@
         <v>7</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Y10" s="4">
         <v>60</v>
@@ -2108,10 +2147,10 @@
         <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2120,10 +2159,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K11" s="4">
         <v>1.5</v>
@@ -2138,10 +2177,10 @@
         <v>0.9</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q11" s="4">
         <v>0</v>
@@ -2150,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T11" s="4">
         <v>0</v>
@@ -2174,10 +2213,10 @@
         <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2186,10 +2225,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2204,10 +2243,10 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q12" s="4">
         <v>5</v>
@@ -2216,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T12" s="4">
         <v>0</v>
@@ -2225,7 +2264,7 @@
         <v>40</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Z12" s="4">
         <v>0</v>
@@ -2246,11 +2285,11 @@
         <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F13" s="4">
         <v>1</v>
       </c>
@@ -2258,10 +2297,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
@@ -2276,10 +2315,10 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q13" s="4">
         <v>10</v>
@@ -2288,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="T13" s="4">
         <v>0</v>
@@ -2297,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Y13" s="4">
         <v>0</v>
@@ -2323,45 +2362,44 @@
         <v>10001</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="Q14" s="4">
         <v>0</v>
       </c>
       <c r="R14" s="4">
         <v>0</v>
       </c>
-      <c r="S14" s="4"/>
       <c r="T14" s="4">
         <v>0.8</v>
       </c>
@@ -2369,10 +2407,10 @@
         <v>2</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Y14" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,25 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
+    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -347,7 +334,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -371,6 +358,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -384,6 +399,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -423,21 +446,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -488,28 +496,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -530,13 +517,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,24 +583,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -590,18 +625,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -614,36 +637,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -662,19 +661,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -723,6 +710,21 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -756,21 +758,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -827,148 +814,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -995,52 +982,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1677,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:29">
@@ -1748,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="AC5" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:29">
@@ -1819,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:28">

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
+    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -334,7 +347,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -358,34 +371,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -399,14 +384,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -446,6 +423,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -496,7 +488,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,49 +530,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,97 +668,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,21 +723,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -758,6 +756,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -814,148 +827,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -982,52 +995,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -300,6 +300,15 @@
   </si>
   <si>
     <t>[0.5]</t>
+  </si>
+  <si>
+    <t>风雷穿刺</t>
+  </si>
+  <si>
+    <t>Archerskill_06</t>
+  </si>
+  <si>
+    <t>FengLeiChuanCi</t>
   </si>
   <si>
     <t>火灵咒</t>
@@ -1311,7 +1320,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -2138,19 +2147,19 @@
     </row>
     <row r="11" customHeight="1" spans="1:28">
       <c r="A11" s="3">
-        <v>2001</v>
+        <v>1005</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3">
-        <v>2001</v>
+        <v>1005</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2161,62 +2170,64 @@
       <c r="H11" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="I11" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="J11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="4">
+        <v>2</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
+        <v>25</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K11" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="4">
-        <v>10</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="Q11" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R11" s="4">
         <v>0</v>
       </c>
-      <c r="S11" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="T11" s="4">
-        <v>0</v>
-      </c>
-      <c r="U11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>60</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>0.8</v>
+      </c>
       <c r="AB11" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:28">
       <c r="A12" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
       </c>
       <c r="C12" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2228,45 +2239,39 @@
         <v>70</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K12" s="4">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M12" s="4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="Q12" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R12" s="4">
         <v>0</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="T12" s="4">
         <v>0</v>
       </c>
       <c r="U12" s="4">
-        <v>40</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z12" s="4">
         <v>0</v>
       </c>
       <c r="AA12" s="4"/>
@@ -2276,19 +2281,19 @@
     </row>
     <row r="13" customHeight="1" spans="1:28">
       <c r="A13" s="3">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
       </c>
       <c r="C13" s="3">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2300,13 +2305,13 @@
         <v>70</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
       </c>
       <c r="L13" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M13" s="4">
         <v>35</v>
@@ -2315,57 +2320,52 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>5</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4">
+        <v>40</v>
+      </c>
+      <c r="W13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="P13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>10</v>
-      </c>
-      <c r="R13" s="4">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="T13" s="4">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4">
-        <v>0</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y13" s="4">
-        <v>0</v>
-      </c>
       <c r="Z13" s="4">
         <v>0</v>
       </c>
-      <c r="AA13" s="4">
-        <v>0</v>
-      </c>
+      <c r="AA13" s="4"/>
       <c r="AB13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="3">
-        <v>10001</v>
+        <v>2003</v>
       </c>
       <c r="B14" s="3">
-        <v>1005</v>
+        <v>2</v>
       </c>
       <c r="C14" s="3">
-        <v>10001</v>
+        <v>2003</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -2377,51 +2377,128 @@
         <v>70</v>
       </c>
       <c r="J14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K14" s="4">
+        <v>5</v>
+      </c>
+      <c r="L14" s="4">
+        <v>10</v>
+      </c>
+      <c r="M14" s="4">
+        <v>35</v>
+      </c>
+      <c r="N14" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>10</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="T14" s="4">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:28">
+      <c r="A15" s="3">
+        <v>10001</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1005</v>
+      </c>
+      <c r="C15" s="3">
+        <v>10001</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4">
-        <v>0</v>
-      </c>
-      <c r="T14" s="4">
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
         <v>0.8</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U15" s="4">
         <v>2</v>
       </c>
-      <c r="V14" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="W14" s="4" t="s">
+      <c r="V15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="W15" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="Y14" s="4">
+      <c r="Y15" s="4">
         <v>50</v>
       </c>
-      <c r="Z14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="4">
+      <c r="Z15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="4">
         <v>0</v>
       </c>
     </row>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="107">
   <si>
     <t>ID</t>
   </si>
@@ -275,21 +275,12 @@
     <t>[1]</t>
   </si>
   <si>
-    <t>剑刃噬心</t>
+    <t>沉天陨击</t>
   </si>
   <si>
     <t>对自身周围造成范围伤害</t>
   </si>
   <si>
-    <t>Warriorskill_35</t>
-  </si>
-  <si>
-    <t>JianRenShiXin</t>
-  </si>
-  <si>
-    <t>沉天陨击</t>
-  </si>
-  <si>
     <t>Priestskill_28</t>
   </si>
   <si>
@@ -309,6 +300,12 @@
   </si>
   <si>
     <t>FengLeiChuanCi</t>
+  </si>
+  <si>
+    <t>(0,0.7,2)</t>
+  </si>
+  <si>
+    <t>[0.2,0.2,0.3,0.3,0.3,0.3,0.4]</t>
   </si>
   <si>
     <t>火灵咒</t>
@@ -1320,7 +1317,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1342,7 +1339,7 @@
     <col min="20" max="20" width="10.25" style="4" customWidth="1"/>
     <col min="21" max="21" width="9.625" style="4" customWidth="1"/>
     <col min="22" max="22" width="10.25" style="4" customWidth="1"/>
-    <col min="23" max="23" width="18.125" style="4" customWidth="1"/>
+    <col min="23" max="23" width="20.1166666666667" style="4" customWidth="1"/>
     <col min="24" max="24" width="9" style="4" customWidth="1"/>
     <col min="25" max="26" width="9" style="4"/>
     <col min="27" max="27" width="12" customWidth="1"/>
@@ -2002,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="3">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>82</v>
@@ -2026,7 +2023,7 @@
         <v>63</v>
       </c>
       <c r="K9" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L9" s="4">
         <v>0</v>
@@ -2050,7 +2047,16 @@
         <v>73</v>
       </c>
       <c r="T9" s="4">
-        <v>0.5</v>
+        <v>2</v>
+      </c>
+      <c r="U9" s="4">
+        <v>7</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="Y9" s="4">
         <v>60</v>
@@ -2065,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:28">
+    <row r="10" customHeight="1" spans="1:29">
       <c r="A10" s="3">
         <v>1004</v>
       </c>
@@ -2073,10 +2079,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="3">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>83</v>
@@ -2091,13 +2097,13 @@
         <v>70</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>63</v>
       </c>
       <c r="K10" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4">
         <v>0</v>
@@ -2109,31 +2115,28 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q10" s="4">
+        <v>5</v>
+      </c>
+      <c r="R10" s="4">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="U10" s="4">
+        <v>3</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y10" s="4">
         <v>10</v>
-      </c>
-      <c r="R10" s="4">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="T10" s="4">
-        <v>2</v>
-      </c>
-      <c r="U10" s="4">
-        <v>7</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="W10" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y10" s="4">
-        <v>60</v>
       </c>
       <c r="Z10" s="4">
         <v>0</v>
@@ -2143,23 +2146,26 @@
       </c>
       <c r="AB10" s="4">
         <v>0</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>7</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:28">
       <c r="A11" s="3">
-        <v>1005</v>
+        <v>2001</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="3">
-        <v>1005</v>
+        <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2170,64 +2176,62 @@
       <c r="H11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="J11" s="4" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="K11" s="4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11" s="4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q11" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R11" s="4">
         <v>0</v>
       </c>
+      <c r="S11" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="T11" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="4">
-        <v>60</v>
-      </c>
-      <c r="Z11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="4">
-        <v>0.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="4"/>
       <c r="AB11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:28">
       <c r="A12" s="3">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
       </c>
       <c r="C12" s="3">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2239,39 +2243,45 @@
         <v>70</v>
       </c>
       <c r="J12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="4">
+        <v>5</v>
+      </c>
+      <c r="L12" s="4">
+        <v>20</v>
+      </c>
+      <c r="M12" s="4">
+        <v>35</v>
+      </c>
+      <c r="N12" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="O12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="K12" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="L12" s="4">
-        <v>10</v>
-      </c>
-      <c r="M12" s="4">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="O12" s="4" t="s">
+      <c r="P12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>5</v>
+      </c>
+      <c r="R12" s="4">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="P12" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="T12" s="4">
         <v>0</v>
       </c>
       <c r="U12" s="4">
+        <v>40</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z12" s="4">
         <v>0</v>
       </c>
       <c r="AA12" s="4"/>
@@ -2281,19 +2291,19 @@
     </row>
     <row r="13" customHeight="1" spans="1:28">
       <c r="A13" s="3">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
       </c>
       <c r="C13" s="3">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2305,13 +2315,13 @@
         <v>70</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
       </c>
       <c r="L13" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M13" s="4">
         <v>35</v>
@@ -2320,52 +2330,57 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="Q13" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R13" s="4">
         <v>0</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="T13" s="4">
         <v>0</v>
       </c>
       <c r="U13" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>0</v>
       </c>
       <c r="Z13" s="4">
         <v>0</v>
       </c>
-      <c r="AA13" s="4"/>
+      <c r="AA13" s="4">
+        <v>0</v>
+      </c>
       <c r="AB13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="3">
-        <v>2003</v>
+        <v>10001</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1005</v>
       </c>
       <c r="C14" s="3">
-        <v>2003</v>
+        <v>10001</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -2377,128 +2392,51 @@
         <v>70</v>
       </c>
       <c r="J14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K14" s="4">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="K14" s="4">
-        <v>5</v>
-      </c>
-      <c r="L14" s="4">
-        <v>10</v>
-      </c>
-      <c r="M14" s="4">
-        <v>35</v>
-      </c>
-      <c r="N14" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="Q14" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R14" s="4">
         <v>0</v>
       </c>
-      <c r="S14" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="T14" s="4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="U14" s="4">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="V14" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="Y14" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Z14" s="4">
         <v>0</v>
       </c>
       <c r="AA14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:28">
-      <c r="A15" s="3">
-        <v>10001</v>
-      </c>
-      <c r="B15" s="3">
-        <v>1005</v>
-      </c>
-      <c r="C15" s="3">
-        <v>10001</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" s="4">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4">
-        <v>0</v>
-      </c>
-      <c r="M15" s="4">
-        <v>0</v>
-      </c>
-      <c r="N15" s="4">
-        <v>0</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>0</v>
-      </c>
-      <c r="R15" s="4">
-        <v>0</v>
-      </c>
-      <c r="T15" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="U15" s="4">
-        <v>2</v>
-      </c>
-      <c r="V15" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="W15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y15" s="4">
-        <v>50</v>
-      </c>
-      <c r="Z15" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="4">
         <v>0</v>
       </c>
     </row>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,25 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
+    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -356,7 +343,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -380,6 +367,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -393,6 +408,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -432,21 +455,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -497,28 +505,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -539,13 +526,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -563,24 +592,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -599,18 +634,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -623,36 +646,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -671,19 +670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -732,6 +719,21 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -765,21 +767,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -836,148 +823,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1004,52 +991,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -2457,7 +2444,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="4">
         <v>0</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="108">
   <si>
     <t>ID</t>
   </si>
@@ -254,6 +254,9 @@
     <t>(0,0,1)</t>
   </si>
   <si>
+    <t>[0.45]</t>
+  </si>
+  <si>
     <t>龙牙猛击</t>
   </si>
   <si>
@@ -266,10 +269,10 @@
     <t>LongYaMengJi</t>
   </si>
   <si>
-    <t>(0,1.1,2.45)</t>
-  </si>
-  <si>
-    <t>[0.6]</t>
+    <t>(0,0.7,2)</t>
+  </si>
+  <si>
+    <t>[0.65]</t>
   </si>
   <si>
     <t>[1]</t>
@@ -290,64 +293,64 @@
     <t>(0,0,1.5)</t>
   </si>
   <si>
+    <t>[0.9]</t>
+  </si>
+  <si>
+    <t>风雷穿刺</t>
+  </si>
+  <si>
+    <t>Archerskill_06</t>
+  </si>
+  <si>
+    <t>FengLeiChuanCi</t>
+  </si>
+  <si>
+    <t>[0.25,0.2,0.3,0.3,0.3,0.3,0.4]</t>
+  </si>
+  <si>
+    <t>火灵咒</t>
+  </si>
+  <si>
+    <t>法师的基础法术，无消耗</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Intonate</t>
+  </si>
+  <si>
+    <t>Effects/Hits/Explosion</t>
+  </si>
+  <si>
+    <t>南明离火</t>
+  </si>
+  <si>
+    <t>对目标位置造成范围法术伤害</t>
+  </si>
+  <si>
+    <t>[0.2]</t>
+  </si>
+  <si>
+    <t>自定义技能</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>哥布林近战</t>
+  </si>
+  <si>
+    <t>哥布林近战物理攻击</t>
+  </si>
+  <si>
+    <t>(0,0.2,2)</t>
+  </si>
+  <si>
     <t>[0.5]</t>
-  </si>
-  <si>
-    <t>风雷穿刺</t>
-  </si>
-  <si>
-    <t>Archerskill_06</t>
-  </si>
-  <si>
-    <t>FengLeiChuanCi</t>
-  </si>
-  <si>
-    <t>(0,0.7,2)</t>
-  </si>
-  <si>
-    <t>[0.2,0.2,0.3,0.3,0.3,0.3,0.4]</t>
-  </si>
-  <si>
-    <t>火灵咒</t>
-  </si>
-  <si>
-    <t>法师的基础法术，无消耗</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Intonate</t>
-  </si>
-  <si>
-    <t>Effects/Hits/Explosion</t>
-  </si>
-  <si>
-    <t>南明离火</t>
-  </si>
-  <si>
-    <t>对目标位置造成范围法术伤害</t>
-  </si>
-  <si>
-    <t>[0.2]</t>
-  </si>
-  <si>
-    <t>自定义技能</t>
-  </si>
-  <si>
-    <t>Position</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>哥布林近战</t>
-  </si>
-  <si>
-    <t>哥布林近战物理攻击</t>
-  </si>
-  <si>
-    <t>(0,0.2,2)</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1342,7 @@
     <col min="20" max="20" width="10.25" style="4" customWidth="1"/>
     <col min="21" max="21" width="9.625" style="4" customWidth="1"/>
     <col min="22" max="22" width="10.25" style="4" customWidth="1"/>
-    <col min="23" max="23" width="20.1166666666667" style="4" customWidth="1"/>
+    <col min="23" max="23" width="21.5333333333333" style="4" customWidth="1"/>
     <col min="24" max="24" width="9" style="4" customWidth="1"/>
     <col min="25" max="26" width="9" style="4"/>
     <col min="27" max="27" width="12" customWidth="1"/>
@@ -1828,7 +1831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" customHeight="1" spans="1:29">
       <c r="A7" s="3">
         <v>1001</v>
       </c>
@@ -1893,7 +1896,7 @@
         <v>74</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Y7" s="4">
         <v>20</v>
@@ -1907,8 +1910,11 @@
       <c r="AB7" s="4">
         <v>0</v>
       </c>
+      <c r="AC7" s="4">
+        <v>11</v>
+      </c>
     </row>
-    <row r="8" customHeight="1" spans="1:28">
+    <row r="8" customHeight="1" spans="1:29">
       <c r="A8" s="3">
         <v>1002</v>
       </c>
@@ -1919,10 +1925,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1934,7 +1940,7 @@
         <v>70</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>63</v>
@@ -1952,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
@@ -1970,13 +1976,13 @@
         <v>3</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y8" s="4">
         <v>40</v>
@@ -1990,8 +1996,11 @@
       <c r="AB8" s="4">
         <v>0</v>
       </c>
+      <c r="AC8" s="4">
+        <v>12</v>
+      </c>
     </row>
-    <row r="9" customHeight="1" spans="1:28">
+    <row r="9" customHeight="1" spans="1:29">
       <c r="A9" s="3">
         <v>1003</v>
       </c>
@@ -2002,10 +2011,10 @@
         <v>1004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -2017,13 +2026,13 @@
         <v>70</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>63</v>
       </c>
       <c r="K9" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" s="4">
         <v>0</v>
@@ -2035,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2053,10 +2062,10 @@
         <v>7</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y9" s="4">
         <v>60</v>
@@ -2069,6 +2078,9 @@
       </c>
       <c r="AB9" s="4">
         <v>0</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:29">
@@ -2082,10 +2094,10 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2097,7 +2109,7 @@
         <v>70</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>63</v>
@@ -2115,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="4">
         <v>5</v>
@@ -2130,7 +2142,7 @@
         <v>3</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="W10" s="4" t="s">
         <v>92</v>
@@ -2425,7 +2437,7 @@
         <v>106</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="Y14" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="107">
   <si>
     <t>ID</t>
   </si>
@@ -254,7 +254,7 @@
     <t>(0,0,1)</t>
   </si>
   <si>
-    <t>[0.45]</t>
+    <t>[0.4]</t>
   </si>
   <si>
     <t>龙牙猛击</t>
@@ -272,9 +272,6 @@
     <t>(0,0.7,2)</t>
   </si>
   <si>
-    <t>[0.65]</t>
-  </si>
-  <si>
     <t>[1]</t>
   </si>
   <si>
@@ -293,7 +290,7 @@
     <t>(0,0,1.5)</t>
   </si>
   <si>
-    <t>[0.9]</t>
+    <t>[0.6]</t>
   </si>
   <si>
     <t>风雷穿刺</t>
@@ -305,7 +302,7 @@
     <t>FengLeiChuanCi</t>
   </si>
   <si>
-    <t>[0.25,0.2,0.3,0.3,0.3,0.3,0.4]</t>
+    <t>[0.2,0.2,0.3,0.3,0.3,0.3,0.4]</t>
   </si>
   <si>
     <t>火灵咒</t>
@@ -1680,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="AA4" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB4" s="4">
         <v>0</v>
@@ -1751,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="4">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="4">
         <v>0</v>
@@ -1899,19 +1896,19 @@
         <v>75</v>
       </c>
       <c r="Y7" s="4">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="Z7" s="4">
         <v>0</v>
       </c>
       <c r="AA7" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="4">
         <v>0</v>
       </c>
       <c r="AC7" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:29">
@@ -1979,25 +1976,25 @@
         <v>80</v>
       </c>
       <c r="W8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="X8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="X8" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="Y8" s="4">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="Z8" s="4">
         <v>0</v>
       </c>
       <c r="AA8" s="4">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="4">
         <v>0</v>
       </c>
       <c r="AC8" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:29">
@@ -2011,10 +2008,10 @@
         <v>1004</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -2026,13 +2023,13 @@
         <v>70</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>63</v>
       </c>
       <c r="K9" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L9" s="4">
         <v>0</v>
@@ -2044,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2062,25 +2059,25 @@
         <v>7</v>
       </c>
       <c r="V9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="W9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="W9" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="Y9" s="4">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="Z9" s="4">
         <v>0</v>
       </c>
       <c r="AA9" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB9" s="4">
         <v>0</v>
       </c>
       <c r="AC9" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:29">
@@ -2094,10 +2091,10 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2109,13 +2106,13 @@
         <v>70</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>63</v>
       </c>
       <c r="K10" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L10" s="4">
         <v>0</v>
@@ -2127,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q10" s="4">
         <v>5</v>
@@ -2145,16 +2142,16 @@
         <v>80</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y10" s="4">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="Z10" s="4">
         <v>0</v>
       </c>
       <c r="AA10" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="4">
         <v>0</v>
@@ -2174,10 +2171,10 @@
         <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2189,7 +2186,7 @@
         <v>70</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K11" s="4">
         <v>1.5</v>
@@ -2204,19 +2201,19 @@
         <v>0.9</v>
       </c>
       <c r="O11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="T11" s="4">
         <v>0</v>
@@ -2240,10 +2237,10 @@
         <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2255,7 +2252,7 @@
         <v>70</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2270,10 +2267,10 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q12" s="4">
         <v>5</v>
@@ -2282,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T12" s="4">
         <v>0</v>
@@ -2291,7 +2288,7 @@
         <v>40</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Z12" s="4">
         <v>0</v>
@@ -2312,10 +2309,10 @@
         <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2327,7 +2324,7 @@
         <v>70</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
@@ -2342,10 +2339,10 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q13" s="4">
         <v>10</v>
@@ -2363,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y13" s="4">
         <v>0</v>
@@ -2389,10 +2386,10 @@
         <v>10001</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -2407,7 +2404,7 @@
         <v>63</v>
       </c>
       <c r="K14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="4">
         <v>0</v>
@@ -2419,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q14" s="4">
         <v>0</v>
@@ -2428,16 +2425,16 @@
         <v>0</v>
       </c>
       <c r="T14" s="4">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="U14" s="4">
         <v>2</v>
       </c>
       <c r="V14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="W14" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="W14" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="Y14" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -83,9 +83,6 @@
     <t>MissileUnitId</t>
   </si>
   <si>
-    <t>HitArt</t>
-  </si>
-  <si>
     <t>Duration</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>投射物UnitId</t>
   </si>
   <si>
-    <t>击中效果</t>
-  </si>
-  <si>
     <t>持续时间</t>
   </si>
   <si>
@@ -248,9 +242,6 @@
     <t>JianHengJi</t>
   </si>
   <si>
-    <t>Effects/Hits/Holy hit</t>
-  </si>
-  <si>
     <t>(0,0,1)</t>
   </si>
   <si>
@@ -315,9 +306,6 @@
   </si>
   <si>
     <t>Intonate</t>
-  </si>
-  <si>
-    <t>Effects/Hits/Explosion</t>
   </si>
   <si>
     <t>南明离火</t>
@@ -1317,7 +1305,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -1335,20 +1323,19 @@
     <col min="16" max="16" width="31.125" style="4" customWidth="1"/>
     <col min="17" max="17" width="10.875" style="4" customWidth="1"/>
     <col min="18" max="18" width="16.4666666666667" style="4" customWidth="1"/>
-    <col min="19" max="19" width="25.575" style="4" customWidth="1"/>
-    <col min="20" max="20" width="10.25" style="4" customWidth="1"/>
-    <col min="21" max="21" width="9.625" style="4" customWidth="1"/>
-    <col min="22" max="22" width="10.25" style="4" customWidth="1"/>
-    <col min="23" max="23" width="21.5333333333333" style="4" customWidth="1"/>
-    <col min="24" max="24" width="9" style="4" customWidth="1"/>
-    <col min="25" max="26" width="9" style="4"/>
-    <col min="27" max="27" width="12" customWidth="1"/>
-    <col min="28" max="28" width="9" style="4"/>
-    <col min="29" max="29" width="13.45" style="4" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="4"/>
+    <col min="19" max="19" width="10.25" style="4" customWidth="1"/>
+    <col min="20" max="20" width="9.625" style="4" customWidth="1"/>
+    <col min="21" max="21" width="10.25" style="4" customWidth="1"/>
+    <col min="22" max="22" width="21.5333333333333" style="4" customWidth="1"/>
+    <col min="23" max="23" width="9" style="4" customWidth="1"/>
+    <col min="24" max="25" width="9" style="4"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="9" style="4"/>
+    <col min="28" max="28" width="13.45" style="4" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:29">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1433,189 +1420,180 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:29">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="Y2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>31</v>
+      <c r="B3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:29">
-      <c r="A3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:29">
+    <row r="4" customHeight="1" spans="1:28">
       <c r="A4" s="3">
         <v>101</v>
       </c>
@@ -1626,67 +1604,67 @@
         <v>101</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="T4" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="U4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="U4" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>65</v>
+      <c r="X4" s="4">
+        <v>100</v>
       </c>
       <c r="Y4" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:29">
+    <row r="5" customHeight="1" spans="1:28">
       <c r="A5" s="3">
         <v>102</v>
       </c>
@@ -1697,7 +1675,7 @@
         <v>102</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -1706,58 +1684,58 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="T5" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="U5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="V5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="U5" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>65</v>
+      <c r="X5" s="4">
+        <v>100</v>
       </c>
       <c r="Y5" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:29">
+    <row r="6" customHeight="1" spans="1:28">
       <c r="A6" s="3">
         <v>103</v>
       </c>
@@ -1768,7 +1746,7 @@
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1777,58 +1755,58 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="T6" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="U6" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="V6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="4">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="U6" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>65</v>
+      <c r="X6" s="4">
+        <v>100</v>
       </c>
       <c r="Y6" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA6" s="4">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:29">
+    <row r="7" customHeight="1" spans="1:28">
       <c r="A7" s="3">
         <v>1001</v>
       </c>
@@ -1839,10 +1817,10 @@
         <v>1001</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1851,13 +1829,13 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K7" s="4">
         <v>1.5</v>
@@ -1872,46 +1850,43 @@
         <v>0</v>
       </c>
       <c r="P7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="T7" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="V7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="U7" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="W7" s="4" t="s">
-        <v>75</v>
+      <c r="X7" s="4">
+        <v>200</v>
       </c>
       <c r="Y7" s="4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:29">
+    <row r="8" customHeight="1" spans="1:28">
       <c r="A8" s="3">
         <v>1002</v>
       </c>
@@ -1922,10 +1897,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1934,13 +1909,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K8" s="4">
         <v>3</v>
@@ -1955,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
@@ -1963,41 +1938,38 @@
       <c r="R8" s="4">
         <v>0</v>
       </c>
-      <c r="S8" s="4" t="s">
-        <v>73</v>
+      <c r="S8" s="4">
+        <v>1</v>
       </c>
       <c r="T8" s="4">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4">
         <v>3</v>
       </c>
+      <c r="U8" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="V8" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="X8" s="4">
+        <v>300</v>
       </c>
       <c r="Y8" s="4">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:29">
+    <row r="9" customHeight="1" spans="1:28">
       <c r="A9" s="3">
         <v>1003</v>
       </c>
@@ -2008,10 +1980,10 @@
         <v>1004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -2020,13 +1992,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K9" s="4">
         <v>7</v>
@@ -2041,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2049,38 +2021,35 @@
       <c r="R9" s="4">
         <v>0</v>
       </c>
-      <c r="S9" s="4" t="s">
-        <v>73</v>
+      <c r="S9" s="4">
+        <v>2</v>
       </c>
       <c r="T9" s="4">
-        <v>2</v>
-      </c>
-      <c r="U9" s="4">
         <v>7</v>
       </c>
+      <c r="U9" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="V9" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="X9" s="4">
+        <v>500</v>
       </c>
       <c r="Y9" s="4">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:29">
+    <row r="10" customHeight="1" spans="1:28">
       <c r="A10" s="3">
         <v>1004</v>
       </c>
@@ -2091,10 +2060,10 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2103,13 +2072,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K10" s="4">
         <v>7</v>
@@ -2124,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q10" s="4">
         <v>5</v>
@@ -2132,35 +2101,35 @@
       <c r="R10" s="4">
         <v>0</v>
       </c>
+      <c r="S10" s="4">
+        <v>2.2</v>
+      </c>
       <c r="T10" s="4">
-        <v>2.2</v>
-      </c>
-      <c r="U10" s="4">
         <v>3</v>
       </c>
+      <c r="U10" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="V10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="W10" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="X10" s="4">
+        <v>200</v>
       </c>
       <c r="Y10" s="4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:28">
+    <row r="11" customHeight="1" spans="1:27">
       <c r="A11" s="3">
         <v>2001</v>
       </c>
@@ -2171,10 +2140,10 @@
         <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2183,10 +2152,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K11" s="4">
         <v>1.5</v>
@@ -2201,10 +2170,10 @@
         <v>0.9</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q11" s="4">
         <v>0</v>
@@ -2212,21 +2181,18 @@
       <c r="R11" s="4">
         <v>0</v>
       </c>
-      <c r="S11" s="4" t="s">
-        <v>96</v>
+      <c r="S11" s="4">
+        <v>0</v>
       </c>
       <c r="T11" s="4">
         <v>0</v>
       </c>
-      <c r="U11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="4"/>
-      <c r="AB11" s="4">
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:28">
+    <row r="12" customHeight="1" spans="1:27">
       <c r="A12" s="3">
         <v>2002</v>
       </c>
@@ -2237,10 +2203,10 @@
         <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -2249,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2267,10 +2233,10 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q12" s="4">
         <v>5</v>
@@ -2278,27 +2244,24 @@
       <c r="R12" s="4">
         <v>0</v>
       </c>
-      <c r="S12" s="4" t="s">
-        <v>96</v>
+      <c r="S12" s="4">
+        <v>0</v>
       </c>
       <c r="T12" s="4">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4">
         <v>40</v>
       </c>
-      <c r="W12" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z12" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4">
+      <c r="V12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:28">
+    <row r="13" customHeight="1" spans="1:27">
       <c r="A13" s="3">
         <v>2003</v>
       </c>
@@ -2309,10 +2272,10 @@
         <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
@@ -2321,10 +2284,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
@@ -2339,10 +2302,10 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="Q13" s="4">
         <v>10</v>
@@ -2350,17 +2313,17 @@
       <c r="R13" s="4">
         <v>0</v>
       </c>
-      <c r="S13" s="4" t="s">
-        <v>73</v>
+      <c r="S13" s="4">
+        <v>0</v>
       </c>
       <c r="T13" s="4">
         <v>0</v>
       </c>
-      <c r="U13" s="4">
-        <v>0</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>99</v>
+      <c r="V13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="X13" s="4">
+        <v>0</v>
       </c>
       <c r="Y13" s="4">
         <v>0</v>
@@ -2371,11 +2334,8 @@
       <c r="AA13" s="4">
         <v>0</v>
       </c>
-      <c r="AB13" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" customHeight="1" spans="1:27">
       <c r="A14" s="3">
         <v>10001</v>
       </c>
@@ -2386,10 +2346,10 @@
         <v>10001</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -2398,10 +2358,10 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K14" s="4">
         <v>2</v>
@@ -2416,36 +2376,36 @@
         <v>0</v>
       </c>
       <c r="P14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="T14" s="4">
+        <v>2</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="V14" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="Q14" s="4">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4">
-        <v>0</v>
-      </c>
-      <c r="T14" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="U14" s="4">
-        <v>2</v>
-      </c>
-      <c r="V14" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="W14" s="4" t="s">
-        <v>106</v>
+      <c r="X14" s="4">
+        <v>50</v>
       </c>
       <c r="Y14" s="4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="4">
         <v>0</v>
       </c>
     </row>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -218,15 +218,21 @@
     <t>(0,1.2,2)</t>
   </si>
   <si>
-    <t>[0.3]</t>
+    <t>[0.15]</t>
   </si>
   <si>
     <t>剑士基础连招二</t>
   </si>
   <si>
+    <t>[0.25]</t>
+  </si>
+  <si>
     <t>剑士基础连招三</t>
   </si>
   <si>
+    <t>[0.2]</t>
+  </si>
+  <si>
     <t>横剑击</t>
   </si>
   <si>
@@ -312,9 +318,6 @@
   </si>
   <si>
     <t>对目标位置造成范围法术伤害</t>
-  </si>
-  <si>
-    <t>[0.2]</t>
   </si>
   <si>
     <t>自定义技能</t>
@@ -1619,7 +1622,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L4" s="4">
         <v>0</v>
@@ -1637,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="4">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="T4" s="4">
         <v>4.5</v>
@@ -1649,7 +1652,7 @@
         <v>63</v>
       </c>
       <c r="X4" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="Y4" s="4">
         <v>0</v>
@@ -1690,7 +1693,7 @@
         <v>61</v>
       </c>
       <c r="K5" s="4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L5" s="4">
         <v>0</v>
@@ -1708,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="4">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="T5" s="4">
         <v>4.5</v>
@@ -1717,10 +1720,10 @@
         <v>62</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="X5" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="Y5" s="4">
         <v>0</v>
@@ -1746,7 +1749,7 @@
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1761,7 +1764,7 @@
         <v>61</v>
       </c>
       <c r="K6" s="4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L6" s="4">
         <v>0</v>
@@ -1779,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="4">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="T6" s="4">
         <v>4.5</v>
@@ -1788,10 +1791,10 @@
         <v>62</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="X6" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="Y6" s="4">
         <v>0</v>
@@ -1817,10 +1820,10 @@
         <v>1001</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1829,10 +1832,10 @@
         <v>3</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>61</v>
@@ -1850,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="4">
         <v>0</v>
@@ -1865,13 +1868,13 @@
         <v>4.5</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="X7" s="4">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y7" s="4">
         <v>0</v>
@@ -1897,10 +1900,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -1909,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>61</v>
@@ -1930,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q8" s="4">
         <v>5</v>
@@ -1945,16 +1948,16 @@
         <v>3</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X8" s="4">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="Y8" s="4">
         <v>0</v>
@@ -1980,10 +1983,10 @@
         <v>1004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -1992,10 +1995,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>61</v>
@@ -2013,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2028,13 +2031,13 @@
         <v>7</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="X9" s="4">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Y9" s="4">
         <v>0</v>
@@ -2060,10 +2063,10 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
@@ -2072,10 +2075,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>61</v>
@@ -2093,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q10" s="4">
         <v>5</v>
@@ -2108,13 +2111,13 @@
         <v>3</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="X10" s="4">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="Y10" s="4">
         <v>0</v>
@@ -2140,10 +2143,10 @@
         <v>2001</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -2152,10 +2155,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K11" s="4">
         <v>1.5</v>
@@ -2170,10 +2173,10 @@
         <v>0.9</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q11" s="4">
         <v>0</v>
@@ -2203,22 +2206,22 @@
         <v>2002</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="K12" s="4">
         <v>5</v>
@@ -2233,10 +2236,10 @@
         <v>1.5</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q12" s="4">
         <v>5</v>
@@ -2251,7 +2254,7 @@
         <v>40</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="Y12" s="4">
         <v>0</v>
@@ -2272,11 +2275,11 @@
         <v>2003</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="F13" s="4">
         <v>1</v>
       </c>
@@ -2284,10 +2287,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K13" s="4">
         <v>5</v>
@@ -2302,10 +2305,10 @@
         <v>1.5</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q13" s="4">
         <v>10</v>
@@ -2320,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="X13" s="4">
         <v>0</v>
@@ -2346,10 +2349,10 @@
         <v>10001</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F14" s="4">
         <v>1</v>
@@ -2358,7 +2361,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>61</v>
@@ -2376,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q14" s="4">
         <v>0</v>
@@ -2391,10 +2394,10 @@
         <v>2</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="X14" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,25 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
+    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -269,9 +256,6 @@
     <t>(0,0.7,2)</t>
   </si>
   <si>
-    <t>[1]</t>
-  </si>
-  <si>
     <t>沉天陨击</t>
   </si>
   <si>
@@ -288,6 +272,9 @@
   </si>
   <si>
     <t>[0.6]</t>
+  </si>
+  <si>
+    <t>[2]</t>
   </si>
   <si>
     <t>风雷穿刺</t>
@@ -344,7 +331,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -368,6 +355,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -381,6 +396,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -420,21 +443,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -485,28 +493,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -527,13 +514,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,24 +580,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -587,18 +622,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -611,36 +634,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -659,19 +658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,6 +707,21 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -753,21 +755,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -824,148 +811,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -992,52 +979,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1953,9 +1940,7 @@
       <c r="V8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="W8" s="4" t="s">
-        <v>80</v>
-      </c>
+      <c r="W8" s="4"/>
       <c r="X8" s="4">
         <v>600</v>
       </c>
@@ -1983,10 +1968,10 @@
         <v>1004</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -1998,7 +1983,7 @@
         <v>70</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>61</v>
@@ -2016,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q9" s="4">
         <v>10</v>
@@ -2031,9 +2016,12 @@
         <v>7</v>
       </c>
       <c r="U9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="V9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="V9" s="4" t="s">
+      <c r="W9" s="4" t="s">
         <v>86</v>
       </c>
       <c r="X9" s="4">
@@ -2066,7 +2054,7 @@
         <v>87</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
+    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -331,7 +344,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -355,34 +368,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -396,14 +381,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -443,6 +420,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -493,7 +485,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -514,49 +527,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,97 +665,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,21 +720,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -755,6 +753,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -811,148 +824,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -979,52 +992,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1609,7 +1622,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L4" s="4">
         <v>0</v>
@@ -1680,7 +1693,7 @@
         <v>61</v>
       </c>
       <c r="K5" s="4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L5" s="4">
         <v>0</v>
@@ -1751,7 +1764,7 @@
         <v>61</v>
       </c>
       <c r="K6" s="4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L6" s="4">
         <v>0</v>
@@ -1940,7 +1953,6 @@
       <c r="V8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="W8" s="4"/>
       <c r="X8" s="4">
         <v>600</v>
       </c>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,25 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
+    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -344,7 +331,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -368,6 +355,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -381,6 +396,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -420,21 +443,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -485,28 +493,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -527,13 +514,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,24 +580,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -587,18 +622,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -611,36 +634,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -659,19 +658,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,6 +707,21 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -753,21 +755,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -824,148 +811,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -992,52 +979,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1874,13 +1861,13 @@
         <v>74</v>
       </c>
       <c r="X7" s="4">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="Y7" s="4">
         <v>0</v>
       </c>
       <c r="Z7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA7" s="4">
         <v>0</v>
@@ -1960,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="4">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" s="4">
         <v>0</v>
@@ -2043,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA9" s="4">
         <v>0</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="4">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA8" s="4">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA9" s="4">
         <v>0</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22920" windowHeight="7190" tabRatio="173"/>
+    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -331,7 +344,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -355,34 +368,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -396,14 +381,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -443,6 +420,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -493,7 +485,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -514,49 +527,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -568,97 +665,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,21 +720,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -755,6 +753,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -811,148 +824,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -979,52 +992,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -2325,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:27">
+    <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="3">
         <v>10001</v>
       </c>
@@ -2397,6 +2410,9 @@
       </c>
       <c r="AA14" s="4">
         <v>0</v>
+      </c>
+      <c r="AB14" s="4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="101">
   <si>
     <t>ID</t>
   </si>
@@ -302,43 +302,34 @@
     <t>[0.2,0.2,0.3,0.3,0.3,0.3,0.4]</t>
   </si>
   <si>
-    <t>火灵咒</t>
-  </si>
-  <si>
-    <t>法师的基础法术，无消耗</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Intonate</t>
-  </si>
-  <si>
-    <t>南明离火</t>
-  </si>
-  <si>
-    <t>对目标位置造成范围法术伤害</t>
-  </si>
-  <si>
-    <t>自定义技能</t>
-  </si>
-  <si>
-    <t>Position</t>
+    <t>哥布林近战</t>
+  </si>
+  <si>
+    <t>哥布林近战物理攻击</t>
   </si>
   <si>
     <t>Attack</t>
   </si>
   <si>
-    <t>哥布林近战</t>
-  </si>
-  <si>
-    <t>哥布林近战物理攻击</t>
-  </si>
-  <si>
     <t>(0,0.2,2)</t>
   </si>
   <si>
     <t>[0.5]</t>
+  </si>
+  <si>
+    <t>骷髅小兵近战</t>
+  </si>
+  <si>
+    <t>骷髅骑士近战1</t>
+  </si>
+  <si>
+    <t>Attack1</t>
+  </si>
+  <si>
+    <t>骷髅骑士近战2</t>
+  </si>
+  <si>
+    <t>Attack2</t>
   </si>
 </sst>
 </file>
@@ -2132,15 +2123,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:27">
+    <row r="11" customHeight="1" spans="1:28">
       <c r="A11" s="3">
-        <v>2001</v>
+        <v>10001</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>1005</v>
       </c>
       <c r="C11" s="3">
-        <v>2001</v>
+        <v>10001</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>91</v>
@@ -2158,59 +2149,71 @@
         <v>70</v>
       </c>
       <c r="J11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="4">
+        <v>2</v>
+      </c>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K11" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="4">
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
+      <c r="S11" s="4">
+        <v>2</v>
+      </c>
+      <c r="T11" s="4">
+        <v>2</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="X11" s="4">
+        <v>50</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="4">
         <v>10</v>
       </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4">
-        <v>0</v>
-      </c>
-      <c r="T11" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4">
-        <v>1</v>
-      </c>
     </row>
-    <row r="12" customHeight="1" spans="1:27">
+    <row r="12" customHeight="1" spans="1:28">
       <c r="A12" s="3">
-        <v>2002</v>
+        <v>10002</v>
       </c>
       <c r="B12" s="3">
-        <v>2</v>
+        <v>1006</v>
       </c>
       <c r="C12" s="3">
-        <v>2002</v>
+        <v>10002</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="3" t="s">
         <v>96</v>
       </c>
+      <c r="E12" s="3"/>
       <c r="F12" s="4">
         <v>1</v>
       </c>
@@ -2221,65 +2224,71 @@
         <v>70</v>
       </c>
       <c r="J12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="4">
+        <v>3</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K12" s="4">
-        <v>5</v>
-      </c>
-      <c r="L12" s="4">
-        <v>20</v>
-      </c>
-      <c r="M12" s="4">
-        <v>35</v>
-      </c>
-      <c r="N12" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="O12" s="4" t="s">
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4">
+        <v>0</v>
+      </c>
+      <c r="S12" s="4">
+        <v>2</v>
+      </c>
+      <c r="T12" s="4">
+        <v>2</v>
+      </c>
+      <c r="U12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="P12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>5</v>
-      </c>
-      <c r="R12" s="4">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4">
-        <v>40</v>
-      </c>
       <c r="V12" s="4" t="s">
-        <v>67</v>
+        <v>95</v>
+      </c>
+      <c r="X12" s="4">
+        <v>50</v>
       </c>
       <c r="Y12" s="4">
         <v>0</v>
       </c>
-      <c r="Z12" s="4"/>
+      <c r="Z12" s="4">
+        <v>1</v>
+      </c>
       <c r="AA12" s="4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="4">
+        <v>10</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:27">
+    <row r="13" customHeight="1" spans="1:28">
       <c r="A13" s="3">
-        <v>2003</v>
+        <v>10003</v>
       </c>
       <c r="B13" s="3">
-        <v>2</v>
+        <v>1007</v>
       </c>
       <c r="C13" s="3">
-        <v>2003</v>
+        <v>10003</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>96</v>
-      </c>
+      <c r="E13" s="3"/>
       <c r="F13" s="4">
         <v>1</v>
       </c>
@@ -2290,70 +2299,71 @@
         <v>70</v>
       </c>
       <c r="J13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="4">
+        <v>3</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K13" s="4">
-        <v>5</v>
-      </c>
-      <c r="L13" s="4">
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="4">
+        <v>2</v>
+      </c>
+      <c r="T13" s="4">
+        <v>2</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="X13" s="4">
+        <v>50</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="4">
         <v>10</v>
-      </c>
-      <c r="M13" s="4">
-        <v>35</v>
-      </c>
-      <c r="N13" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>10</v>
-      </c>
-      <c r="R13" s="4">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4">
-        <v>0</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="X13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="4">
-        <v>0</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="3">
-        <v>10001</v>
+        <v>10004</v>
       </c>
       <c r="B14" s="3">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C14" s="3">
-        <v>10001</v>
+        <v>10004</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>101</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="E14" s="3"/>
       <c r="F14" s="4">
         <v>1</v>
       </c>
@@ -2367,37 +2377,37 @@
         <v>61</v>
       </c>
       <c r="K14" s="4">
+        <v>3</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4">
         <v>2</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>0</v>
-      </c>
-      <c r="R14" s="4">
-        <v>0</v>
-      </c>
-      <c r="S14" s="4">
-        <v>1.7</v>
       </c>
       <c r="T14" s="4">
         <v>2</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="X14" s="4">
         <v>50</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -1643,7 +1643,7 @@
         <v>63</v>
       </c>
       <c r="X4" s="4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="4">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>65</v>
       </c>
       <c r="X5" s="4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="4">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         <v>67</v>
       </c>
       <c r="X6" s="4">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="4">
         <v>0</v>
       </c>
       <c r="Z6" s="4">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AA6" s="4">
         <v>0</v>
@@ -1865,13 +1865,13 @@
         <v>74</v>
       </c>
       <c r="X7" s="4">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="4">
         <v>0</v>
       </c>
       <c r="Z7" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA7" s="4">
         <v>0</v>
@@ -1945,13 +1945,13 @@
         <v>74</v>
       </c>
       <c r="X8" s="4">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="4">
         <v>0</v>
       </c>
       <c r="Z8" s="4">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="4">
         <v>0</v>
@@ -2028,13 +2028,13 @@
         <v>86</v>
       </c>
       <c r="X9" s="4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="4">
         <v>0</v>
       </c>
       <c r="Z9" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="4">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>90</v>
       </c>
       <c r="X10" s="4">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="4">
         <v>0</v>
       </c>
       <c r="Z10" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA10" s="4">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>95</v>
       </c>
       <c r="X11" s="4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="4">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>95</v>
       </c>
       <c r="X12" s="4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="4">
         <v>0</v>
@@ -2335,7 +2335,7 @@
         <v>95</v>
       </c>
       <c r="X13" s="4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="4">
         <v>0</v>
@@ -2410,13 +2410,13 @@
         <v>95</v>
       </c>
       <c r="X14" s="4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="4">
         <v>0</v>
       </c>
       <c r="Z14" s="4">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" s="4">
         <v>0</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,25 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
+    <workbookView windowWidth="20330" windowHeight="7190" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -335,7 +322,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -359,6 +346,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -372,6 +387,14 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -411,21 +434,6 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -476,28 +484,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -518,13 +505,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,24 +571,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -578,18 +613,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -602,36 +625,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -650,19 +649,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -711,6 +698,21 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -744,21 +746,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -815,148 +802,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -983,52 +970,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1655,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AB4" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:28">
@@ -1726,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="AB5" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:28">
@@ -1797,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AB6" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:28">
@@ -1877,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:28">
@@ -1957,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:28">
@@ -2120,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:28">

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -2214,7 +2214,7 @@
         <v>61</v>
       </c>
       <c r="K12" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" s="4">
         <v>0</v>
@@ -2289,7 +2289,7 @@
         <v>61</v>
       </c>
       <c r="K13" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="4">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>61</v>
       </c>
       <c r="K14" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" s="4">
         <v>0</v>

--- a/SERVER/Common/Data/excel/SkillDefine.xlsx
+++ b/SERVER/Common/Data/excel/SkillDefine.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20330" windowHeight="7190" tabRatio="173"/>
+    <workbookView windowWidth="25600" windowHeight="12790" tabRatio="173"/>
   </bookViews>
   <sheets>
     <sheet name="SkillDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -298,7 +311,7 @@
     <t>Attack</t>
   </si>
   <si>
-    <t>(0,0.2,2)</t>
+    <t>(0,0.7,0.7)</t>
   </si>
   <si>
     <t>[0.5]</t>
@@ -307,22 +320,31 @@
     <t>骷髅小兵近战</t>
   </si>
   <si>
+    <t>(0,0.6,1.4)</t>
+  </si>
+  <si>
     <t>骷髅骑士近战1</t>
   </si>
   <si>
     <t>Attack1</t>
   </si>
   <si>
+    <t>(0,0.7,0.6)</t>
+  </si>
+  <si>
     <t>骷髅骑士近战2</t>
   </si>
   <si>
     <t>Attack2</t>
+  </si>
+  <si>
+    <t>(0,0.7,1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -346,34 +368,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -387,14 +381,6 @@
       <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -434,6 +420,21 @@
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -484,7 +485,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -505,49 +527,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,97 +665,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,21 +720,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -746,6 +753,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -802,148 +824,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -970,52 +992,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1600,7 +1622,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="4">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="L4" s="4">
         <v>0</v>
@@ -1671,7 +1693,7 @@
         <v>61</v>
       </c>
       <c r="K5" s="4">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="L5" s="4">
         <v>0</v>
@@ -1742,7 +1764,7 @@
         <v>61</v>
       </c>
       <c r="K6" s="4">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="L6" s="4">
         <v>0</v>
@@ -2163,7 +2185,7 @@
         <v>2</v>
       </c>
       <c r="T11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" s="4" t="s">
         <v>94</v>
@@ -2235,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="S12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" s="4">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="V12" s="4" t="s">
         <v>95</v>
@@ -2273,7 +2295,7 @@
         <v>10003</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="4">
@@ -2301,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q13" s="4">
         <v>0</v>
@@ -2310,13 +2332,13 @@
         <v>0</v>
       </c>
       <c r="S13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" s="4">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="V13" s="4" t="s">
         <v>95</v>
@@ -2348,7 +2370,7 @@
         <v>10004</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="4">
@@ -2376,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q14" s="4">
         <v>0</v>
@@ -2385,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="S14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T14" s="4">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="V14" s="4" t="s">
         <v>95</v>
